--- a/raw/두산.xlsx
+++ b/raw/두산.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/920678a7b799b336/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7680357B-F075-42A7-B850-81315C38B7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{7680357B-F075-42A7-B850-81315C38B7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ECB1F41-2033-4211-B684-F6C10457D52A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F0C2C7D2-7D47-4435-BEFA-4398D2F93944}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="81">
   <si>
     <t>순위</t>
   </si>
@@ -166,11 +166,132 @@
   <si>
     <t>타카다</t>
   </si>
+  <si>
+    <t>고효준</t>
+  </si>
+  <si>
+    <t>콜어빈</t>
+  </si>
+  <si>
+    <t>홍건희</t>
+  </si>
+  <si>
+    <t>홍민규</t>
+  </si>
+  <si>
+    <t>김명신</t>
+  </si>
+  <si>
+    <t>김유성</t>
+  </si>
+  <si>
+    <t>김호준</t>
+  </si>
+  <si>
+    <t>박정수</t>
+  </si>
+  <si>
+    <t>제환유</t>
+  </si>
+  <si>
+    <t>김강률</t>
+  </si>
+  <si>
+    <t>정철원</t>
+  </si>
+  <si>
+    <t>발라조빅</t>
+  </si>
+  <si>
+    <t>브랜든</t>
+  </si>
+  <si>
+    <t>김동주</t>
+  </si>
+  <si>
+    <t>김민규</t>
+  </si>
+  <si>
+    <t>박소준</t>
+  </si>
+  <si>
+    <t>시라카와</t>
+  </si>
+  <si>
+    <t>이교훈</t>
+  </si>
+  <si>
+    <t>알칸타라</t>
+  </si>
+  <si>
+    <t>장원준</t>
+  </si>
+  <si>
+    <t>이형범</t>
+  </si>
+  <si>
+    <t>이승진</t>
+  </si>
+  <si>
+    <t>김지용</t>
+  </si>
+  <si>
+    <t>스탁</t>
+  </si>
+  <si>
+    <t>윤명준</t>
+  </si>
+  <si>
+    <t>임창민</t>
+  </si>
+  <si>
+    <t>전창민</t>
+  </si>
+  <si>
+    <t>박웅</t>
+  </si>
+  <si>
+    <t>이현승</t>
+  </si>
+  <si>
+    <t>권휘</t>
+  </si>
+  <si>
+    <t>미란다</t>
+  </si>
+  <si>
+    <t>박종기</t>
+  </si>
+  <si>
+    <t>유희관</t>
+  </si>
+  <si>
+    <t>김도윤</t>
+  </si>
+  <si>
+    <t>남호</t>
+  </si>
+  <si>
+    <t>로켓</t>
+  </si>
+  <si>
+    <t>유재유</t>
+  </si>
+  <si>
+    <t>현도훈</t>
+  </si>
+  <si>
+    <t>년도</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="180" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -268,7 +389,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -287,10 +408,25 @@
     <xf numFmtId="12" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="12" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -628,12 +764,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD62A5F-BBB2-4435-BEEC-0678F3BDA09E}">
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:T140"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <sheetData>
     <row r="1" spans="1:20" ht="18" thickBot="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -695,7 +831,7 @@
     </row>
     <row r="2" spans="1:20" ht="18" thickBot="1">
       <c r="A2" s="3">
-        <v>1</v>
+        <v>2026</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>20</v>
@@ -757,7 +893,7 @@
     </row>
     <row r="3" spans="1:20" ht="18" thickBot="1">
       <c r="A3" s="3">
-        <v>2</v>
+        <v>2026</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>22</v>
@@ -819,7 +955,7 @@
     </row>
     <row r="4" spans="1:20" ht="18" thickBot="1">
       <c r="A4" s="3">
-        <v>3</v>
+        <v>2026</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>24</v>
@@ -881,7 +1017,7 @@
     </row>
     <row r="5" spans="1:20" ht="18" thickBot="1">
       <c r="A5" s="3">
-        <v>3</v>
+        <v>2026</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>25</v>
@@ -943,7 +1079,7 @@
     </row>
     <row r="6" spans="1:20" ht="18" thickBot="1">
       <c r="A6" s="3">
-        <v>3</v>
+        <v>2026</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>26</v>
@@ -1005,7 +1141,7 @@
     </row>
     <row r="7" spans="1:20" ht="18" thickBot="1">
       <c r="A7" s="3">
-        <v>3</v>
+        <v>2026</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>27</v>
@@ -1067,7 +1203,7 @@
     </row>
     <row r="8" spans="1:20" ht="18" thickBot="1">
       <c r="A8" s="3">
-        <v>7</v>
+        <v>2026</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>28</v>
@@ -1129,7 +1265,7 @@
     </row>
     <row r="9" spans="1:20" ht="18" thickBot="1">
       <c r="A9" s="3">
-        <v>7</v>
+        <v>2026</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>29</v>
@@ -1191,7 +1327,7 @@
     </row>
     <row r="10" spans="1:20" ht="18" thickBot="1">
       <c r="A10" s="3">
-        <v>7</v>
+        <v>2026</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>30</v>
@@ -1253,7 +1389,7 @@
     </row>
     <row r="11" spans="1:20" ht="18" thickBot="1">
       <c r="A11" s="3">
-        <v>7</v>
+        <v>2026</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>31</v>
@@ -1315,7 +1451,7 @@
     </row>
     <row r="12" spans="1:20" ht="18" thickBot="1">
       <c r="A12" s="3">
-        <v>7</v>
+        <v>2026</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>32</v>
@@ -1377,7 +1513,7 @@
     </row>
     <row r="13" spans="1:20" ht="18" thickBot="1">
       <c r="A13" s="3">
-        <v>12</v>
+        <v>2026</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>33</v>
@@ -1439,7 +1575,7 @@
     </row>
     <row r="14" spans="1:20" ht="18" thickBot="1">
       <c r="A14" s="3">
-        <v>12</v>
+        <v>2026</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>34</v>
@@ -1501,7 +1637,7 @@
     </row>
     <row r="15" spans="1:20" ht="18" thickBot="1">
       <c r="A15" s="3">
-        <v>12</v>
+        <v>2026</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>35</v>
@@ -1563,7 +1699,7 @@
     </row>
     <row r="16" spans="1:20" ht="18" thickBot="1">
       <c r="A16" s="3">
-        <v>15</v>
+        <v>2026</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>36</v>
@@ -1625,7 +1761,7 @@
     </row>
     <row r="17" spans="1:20" ht="18" thickBot="1">
       <c r="A17" s="3">
-        <v>15</v>
+        <v>2026</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>37</v>
@@ -1687,7 +1823,7 @@
     </row>
     <row r="18" spans="1:20" ht="18" thickBot="1">
       <c r="A18" s="3">
-        <v>15</v>
+        <v>2026</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>38</v>
@@ -1749,7 +1885,7 @@
     </row>
     <row r="19" spans="1:20" ht="18" thickBot="1">
       <c r="A19" s="3">
-        <v>15</v>
+        <v>2026</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -1811,7 +1947,7 @@
     </row>
     <row r="20" spans="1:20" ht="18" thickBot="1">
       <c r="A20" s="3">
-        <v>15</v>
+        <v>2026</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>40</v>
@@ -1871,9 +2007,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
-      <c r="A21" s="6">
-        <v>15</v>
+    <row r="21" spans="1:20" ht="18" thickBot="1">
+      <c r="A21" s="3">
+        <v>2026</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>41</v>
@@ -1931,6 +2067,7384 @@
       </c>
       <c r="T21" s="6">
         <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="18" thickBot="1">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="18" thickBot="1">
+      <c r="A23" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="4">
+        <v>9</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3.52</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3">
+        <v>1</v>
+      </c>
+      <c r="K23" s="3">
+        <v>32</v>
+      </c>
+      <c r="L23" s="5">
+        <v>7.666666666666667</v>
+      </c>
+      <c r="M23" s="3">
+        <v>8</v>
+      </c>
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
+        <v>2</v>
+      </c>
+      <c r="P23" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3">
+        <v>0.27600000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="18" thickBot="1">
+      <c r="A24" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="4">
+        <v>9</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2.08</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3">
+        <v>1</v>
+      </c>
+      <c r="K24" s="3">
+        <v>37</v>
+      </c>
+      <c r="L24" s="5">
+        <v>8.6666666666666661</v>
+      </c>
+      <c r="M24" s="3">
+        <v>9</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>6</v>
+      </c>
+      <c r="R24" s="3">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3">
+        <v>2</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="18" thickBot="1">
+      <c r="A25" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="4">
+        <v>8</v>
+      </c>
+      <c r="E25" s="3">
+        <v>9</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
+        <v>1</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" s="3">
+        <v>28</v>
+      </c>
+      <c r="L25" s="3">
+        <v>5</v>
+      </c>
+      <c r="M25" s="3">
+        <v>9</v>
+      </c>
+      <c r="N25" s="3">
+        <v>2</v>
+      </c>
+      <c r="O25" s="3">
+        <v>5</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>2</v>
+      </c>
+      <c r="R25" s="3">
+        <v>7</v>
+      </c>
+      <c r="S25" s="3">
+        <v>5</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0.40899999999999997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="18" thickBot="1">
+      <c r="A26" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="4">
+        <v>6</v>
+      </c>
+      <c r="E26" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1</v>
+      </c>
+      <c r="H26" s="3">
+        <v>2</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
+        <v>27</v>
+      </c>
+      <c r="L26" s="5">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="M26" s="3">
+        <v>6</v>
+      </c>
+      <c r="N26" s="3">
+        <v>1</v>
+      </c>
+      <c r="O26" s="3">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>6</v>
+      </c>
+      <c r="R26" s="3">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3">
+        <v>4</v>
+      </c>
+      <c r="T26" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="18" thickBot="1">
+      <c r="A27" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="4">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3">
+        <v>19.29</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>16</v>
+      </c>
+      <c r="L27" s="5">
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="M27" s="3">
+        <v>5</v>
+      </c>
+      <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>1</v>
+      </c>
+      <c r="R27" s="3">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
+        <v>0.45500000000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="18" thickBot="1">
+      <c r="A28" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="4">
+        <v>5</v>
+      </c>
+      <c r="E28" s="3">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K28" s="3">
+        <v>16</v>
+      </c>
+      <c r="L28" s="5">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="M28" s="3">
+        <v>3</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>3</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>1</v>
+      </c>
+      <c r="R28" s="3">
+        <v>1</v>
+      </c>
+      <c r="S28" s="3">
+        <v>1</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="18" thickBot="1">
+      <c r="A29" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="4">
+        <v>5</v>
+      </c>
+      <c r="E29" s="3">
+        <v>9.82</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>1</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>19</v>
+      </c>
+      <c r="L29" s="5">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="M29" s="3">
+        <v>6</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>2</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>7</v>
+      </c>
+      <c r="R29" s="3">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3">
+        <v>4</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0.35299999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="18" thickBot="1">
+      <c r="A30" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="4">
+        <v>4</v>
+      </c>
+      <c r="E30" s="3">
+        <v>5.75</v>
+      </c>
+      <c r="F30" s="3">
+        <v>2</v>
+      </c>
+      <c r="G30" s="3">
+        <v>2</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="K30" s="3">
+        <v>93</v>
+      </c>
+      <c r="L30" s="5">
+        <v>20.333333333333332</v>
+      </c>
+      <c r="M30" s="3">
+        <v>30</v>
+      </c>
+      <c r="N30" s="3">
+        <v>4</v>
+      </c>
+      <c r="O30" s="3">
+        <v>7</v>
+      </c>
+      <c r="P30" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>14</v>
+      </c>
+      <c r="R30" s="3">
+        <v>13</v>
+      </c>
+      <c r="S30" s="3">
+        <v>13</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0.36099999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="18" thickBot="1">
+      <c r="A31" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="4">
+        <v>4</v>
+      </c>
+      <c r="E31" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K31" s="3">
+        <v>21</v>
+      </c>
+      <c r="L31" s="5">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="M31" s="3">
+        <v>5</v>
+      </c>
+      <c r="N31" s="3">
+        <v>1</v>
+      </c>
+      <c r="O31" s="3">
+        <v>4</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>2</v>
+      </c>
+      <c r="R31" s="3">
+        <v>4</v>
+      </c>
+      <c r="S31" s="3">
+        <v>3</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0.313</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="18" thickBot="1">
+      <c r="A32" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="4">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K32" s="3">
+        <v>18</v>
+      </c>
+      <c r="L32" s="5">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="M32" s="3">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>1</v>
+      </c>
+      <c r="P32" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>2</v>
+      </c>
+      <c r="R32" s="3">
+        <v>2</v>
+      </c>
+      <c r="S32" s="3">
+        <v>1</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0.313</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="18" thickBot="1">
+      <c r="A33" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="4">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3">
+        <v>5.82</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1</v>
+      </c>
+      <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
+        <v>72</v>
+      </c>
+      <c r="L33" s="3">
+        <v>17</v>
+      </c>
+      <c r="M33" s="3">
+        <v>13</v>
+      </c>
+      <c r="N33" s="3">
+        <v>2</v>
+      </c>
+      <c r="O33" s="3">
+        <v>7</v>
+      </c>
+      <c r="P33" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>16</v>
+      </c>
+      <c r="R33" s="3">
+        <v>12</v>
+      </c>
+      <c r="S33" s="3">
+        <v>11</v>
+      </c>
+      <c r="T33" s="3">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="18" thickBot="1">
+      <c r="A34" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="4">
+        <v>3</v>
+      </c>
+      <c r="E34" s="3">
+        <v>4.08</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3">
+        <v>1</v>
+      </c>
+      <c r="H34" s="3">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3">
+        <v>68</v>
+      </c>
+      <c r="L34" s="5">
+        <v>17.666666666666668</v>
+      </c>
+      <c r="M34" s="3">
+        <v>13</v>
+      </c>
+      <c r="N34" s="3">
+        <v>2</v>
+      </c>
+      <c r="O34" s="3">
+        <v>6</v>
+      </c>
+      <c r="P34" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>7</v>
+      </c>
+      <c r="R34" s="3">
+        <v>8</v>
+      </c>
+      <c r="S34" s="3">
+        <v>8</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0.217</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="18" thickBot="1">
+      <c r="A35" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="4">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2.08</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
+        <v>1</v>
+      </c>
+      <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
+        <v>33</v>
+      </c>
+      <c r="L35" s="5">
+        <v>8.6666666666666661</v>
+      </c>
+      <c r="M35" s="3">
+        <v>5</v>
+      </c>
+      <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3">
+        <v>2</v>
+      </c>
+      <c r="T35" s="3">
+        <v>0.16700000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="18" thickBot="1">
+      <c r="A36" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="4">
+        <v>2</v>
+      </c>
+      <c r="E36" s="3">
+        <v>2.38</v>
+      </c>
+      <c r="F36" s="3">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3">
+        <v>1</v>
+      </c>
+      <c r="H36" s="3">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3">
+        <v>46</v>
+      </c>
+      <c r="L36" s="5">
+        <v>11.333333333333334</v>
+      </c>
+      <c r="M36" s="3">
+        <v>8</v>
+      </c>
+      <c r="N36" s="3">
+        <v>0</v>
+      </c>
+      <c r="O36" s="3">
+        <v>7</v>
+      </c>
+      <c r="P36" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>11</v>
+      </c>
+      <c r="R36" s="3">
+        <v>3</v>
+      </c>
+      <c r="S36" s="3">
+        <v>3</v>
+      </c>
+      <c r="T36" s="3">
+        <v>0.21099999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="18" thickBot="1">
+      <c r="A37" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="4">
+        <v>2</v>
+      </c>
+      <c r="E37" s="3">
+        <v>11.57</v>
+      </c>
+      <c r="F37" s="3">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K37" s="3">
+        <v>10</v>
+      </c>
+      <c r="L37" s="5">
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="M37" s="3">
+        <v>2</v>
+      </c>
+      <c r="N37" s="3">
+        <v>2</v>
+      </c>
+      <c r="O37" s="3">
+        <v>2</v>
+      </c>
+      <c r="P37" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>1</v>
+      </c>
+      <c r="R37" s="3">
+        <v>3</v>
+      </c>
+      <c r="S37" s="3">
+        <v>3</v>
+      </c>
+      <c r="T37" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="18" thickBot="1">
+      <c r="A38" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="4">
+        <v>2</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3">
+        <v>1</v>
+      </c>
+      <c r="G38" s="3">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3">
+        <v>1</v>
+      </c>
+      <c r="K38" s="3">
+        <v>11</v>
+      </c>
+      <c r="L38" s="5">
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="M38" s="3">
+        <v>2</v>
+      </c>
+      <c r="N38" s="3">
+        <v>0</v>
+      </c>
+      <c r="O38" s="3">
+        <v>1</v>
+      </c>
+      <c r="P38" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>2</v>
+      </c>
+      <c r="R38" s="3">
+        <v>0</v>
+      </c>
+      <c r="S38" s="3">
+        <v>0</v>
+      </c>
+      <c r="T38" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="18" thickBot="1">
+      <c r="A39" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="4">
+        <v>1</v>
+      </c>
+      <c r="E39" s="3">
+        <v>18</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K39" s="3">
+        <v>6</v>
+      </c>
+      <c r="L39" s="3">
+        <v>1</v>
+      </c>
+      <c r="M39" s="3">
+        <v>3</v>
+      </c>
+      <c r="N39" s="3">
+        <v>0</v>
+      </c>
+      <c r="O39" s="3">
+        <v>0</v>
+      </c>
+      <c r="P39" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>0</v>
+      </c>
+      <c r="R39" s="3">
+        <v>2</v>
+      </c>
+      <c r="S39" s="3">
+        <v>2</v>
+      </c>
+      <c r="T39" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="18" thickBot="1">
+      <c r="A40" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="4">
+        <v>1</v>
+      </c>
+      <c r="E40" s="3">
+        <v>3.86</v>
+      </c>
+      <c r="F40" s="3">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K40" s="3">
+        <v>11</v>
+      </c>
+      <c r="L40" s="5">
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="M40" s="3">
+        <v>2</v>
+      </c>
+      <c r="N40" s="3">
+        <v>0</v>
+      </c>
+      <c r="O40" s="3">
+        <v>2</v>
+      </c>
+      <c r="P40" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>5</v>
+      </c>
+      <c r="R40" s="3">
+        <v>1</v>
+      </c>
+      <c r="S40" s="3">
+        <v>1</v>
+      </c>
+      <c r="T40" s="3">
+        <v>0.222</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="18" thickBot="1">
+      <c r="A41" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" s="4">
+        <v>1</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K41" s="3">
+        <v>1</v>
+      </c>
+      <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
+        <v>1</v>
+      </c>
+      <c r="N41" s="3">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+      <c r="R41" s="3">
+        <v>1</v>
+      </c>
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" ht="18" thickBot="1">
+      <c r="A42" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1</v>
+      </c>
+      <c r="E42" s="3">
+        <v>27</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K42" s="3">
+        <v>2</v>
+      </c>
+      <c r="L42" s="8">
+        <v>46025</v>
+      </c>
+      <c r="M42" s="3">
+        <v>1</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>1</v>
+      </c>
+      <c r="S42" s="3">
+        <v>1</v>
+      </c>
+      <c r="T42" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" ht="18" thickBot="1">
+      <c r="A43" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="4">
+        <v>1</v>
+      </c>
+      <c r="E43" s="3">
+        <v>18</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1</v>
+      </c>
+      <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
+        <v>15</v>
+      </c>
+      <c r="L43" s="3">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3">
+        <v>1</v>
+      </c>
+      <c r="O43" s="3">
+        <v>2</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3">
+        <v>6</v>
+      </c>
+      <c r="S43" s="3">
+        <v>6</v>
+      </c>
+      <c r="T43" s="3">
+        <v>0.36399999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" ht="18" thickBot="1">
+      <c r="A44" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="4">
+        <v>1</v>
+      </c>
+      <c r="E44" s="3">
+        <v>67.5</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K44" s="3">
+        <v>7</v>
+      </c>
+      <c r="L44" s="8">
+        <v>46056</v>
+      </c>
+      <c r="M44" s="3">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3">
+        <v>2</v>
+      </c>
+      <c r="O44" s="3">
+        <v>2</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>1</v>
+      </c>
+      <c r="R44" s="3">
+        <v>5</v>
+      </c>
+      <c r="S44" s="3">
+        <v>5</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" ht="18" thickBot="1">
+      <c r="A45" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1.29</v>
+      </c>
+      <c r="F45" s="3">
+        <v>1</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1</v>
+      </c>
+      <c r="K45" s="3">
+        <v>25</v>
+      </c>
+      <c r="L45" s="3">
+        <v>7</v>
+      </c>
+      <c r="M45" s="3">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
+        <v>2</v>
+      </c>
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>6</v>
+      </c>
+      <c r="R45" s="3">
+        <v>1</v>
+      </c>
+      <c r="S45" s="3">
+        <v>1</v>
+      </c>
+      <c r="T45" s="3">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" ht="18" thickBot="1">
+      <c r="A46" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="10">
+        <v>1</v>
+      </c>
+      <c r="E46" s="9">
+        <v>13.5</v>
+      </c>
+      <c r="F46" s="9">
+        <v>0</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0</v>
+      </c>
+      <c r="H46" s="9">
+        <v>0</v>
+      </c>
+      <c r="I46" s="9">
+        <v>0</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K46" s="9">
+        <v>16</v>
+      </c>
+      <c r="L46" s="11">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="M46" s="9">
+        <v>5</v>
+      </c>
+      <c r="N46" s="9">
+        <v>3</v>
+      </c>
+      <c r="O46" s="9">
+        <v>2</v>
+      </c>
+      <c r="P46" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="9">
+        <v>1</v>
+      </c>
+      <c r="R46" s="9">
+        <v>5</v>
+      </c>
+      <c r="S46" s="9">
+        <v>5</v>
+      </c>
+      <c r="T46" s="9">
+        <v>0.38500000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" ht="18" thickBot="1">
+      <c r="A47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T47" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="18" thickBot="1">
+      <c r="A48" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="4">
+        <v>11</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1.54</v>
+      </c>
+      <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
+        <v>2</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K48" s="3">
+        <v>51</v>
+      </c>
+      <c r="L48" s="5">
+        <v>11.666666666666666</v>
+      </c>
+      <c r="M48" s="3">
+        <v>7</v>
+      </c>
+      <c r="N48" s="3">
+        <v>1</v>
+      </c>
+      <c r="O48" s="3">
+        <v>9</v>
+      </c>
+      <c r="P48" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>12</v>
+      </c>
+      <c r="R48" s="3">
+        <v>2</v>
+      </c>
+      <c r="S48" s="3">
+        <v>2</v>
+      </c>
+      <c r="T48" s="3">
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" ht="18" thickBot="1">
+      <c r="A49" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" s="4">
+        <v>9</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K49" s="3">
+        <v>35</v>
+      </c>
+      <c r="L49" s="3">
+        <v>9</v>
+      </c>
+      <c r="M49" s="3">
+        <v>4</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>7</v>
+      </c>
+      <c r="R49" s="3">
+        <v>2</v>
+      </c>
+      <c r="S49" s="3">
+        <v>2</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0.14799999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" ht="18" thickBot="1">
+      <c r="A50" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="4">
+        <v>8</v>
+      </c>
+      <c r="E50" s="3">
+        <v>7.56</v>
+      </c>
+      <c r="F50" s="3">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3">
+        <v>2</v>
+      </c>
+      <c r="H50" s="3">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K50" s="3">
+        <v>44</v>
+      </c>
+      <c r="L50" s="5">
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="M50" s="3">
+        <v>8</v>
+      </c>
+      <c r="N50" s="3">
+        <v>3</v>
+      </c>
+      <c r="O50" s="3">
+        <v>9</v>
+      </c>
+      <c r="P50" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>9</v>
+      </c>
+      <c r="R50" s="3">
+        <v>8</v>
+      </c>
+      <c r="S50" s="3">
+        <v>7</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" ht="18" thickBot="1">
+      <c r="A51" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" s="4">
+        <v>6</v>
+      </c>
+      <c r="E51" s="3">
+        <v>3.86</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3">
+        <v>3</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K51" s="3">
+        <v>19</v>
+      </c>
+      <c r="L51" s="5">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="M51" s="3">
+        <v>6</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>5</v>
+      </c>
+      <c r="R51" s="3">
+        <v>2</v>
+      </c>
+      <c r="S51" s="3">
+        <v>2</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0.316</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" ht="18" thickBot="1">
+      <c r="A52" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" s="4">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3">
+        <v>13.5</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
+        <v>17</v>
+      </c>
+      <c r="L52" s="5">
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="M52" s="3">
+        <v>5</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>4</v>
+      </c>
+      <c r="R52" s="3">
+        <v>4</v>
+      </c>
+      <c r="S52" s="3">
+        <v>4</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0.41699999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" ht="18" thickBot="1">
+      <c r="A53" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" s="4">
+        <v>5</v>
+      </c>
+      <c r="E53" s="3">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <v>1</v>
+      </c>
+      <c r="I53" s="3">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K53" s="3">
+        <v>18</v>
+      </c>
+      <c r="L53" s="3">
+        <v>5</v>
+      </c>
+      <c r="M53" s="3">
+        <v>4</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>5</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0.222</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="18" thickBot="1">
+      <c r="A54" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="4">
+        <v>5</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6.35</v>
+      </c>
+      <c r="F54" s="3">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K54" s="3">
+        <v>29</v>
+      </c>
+      <c r="L54" s="5">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="M54" s="3">
+        <v>10</v>
+      </c>
+      <c r="N54" s="3">
+        <v>2</v>
+      </c>
+      <c r="O54" s="3">
+        <v>4</v>
+      </c>
+      <c r="P54" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>2</v>
+      </c>
+      <c r="R54" s="3">
+        <v>4</v>
+      </c>
+      <c r="S54" s="3">
+        <v>4</v>
+      </c>
+      <c r="T54" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" ht="18" thickBot="1">
+      <c r="A55" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D55" s="4">
+        <v>4</v>
+      </c>
+      <c r="E55" s="3">
+        <v>8.44</v>
+      </c>
+      <c r="F55" s="3">
+        <v>0</v>
+      </c>
+      <c r="G55" s="3">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3">
+        <v>0</v>
+      </c>
+      <c r="I55" s="3">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K55" s="3">
+        <v>23</v>
+      </c>
+      <c r="L55" s="5">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="M55" s="3">
+        <v>6</v>
+      </c>
+      <c r="N55" s="3">
+        <v>1</v>
+      </c>
+      <c r="O55" s="3">
+        <v>2</v>
+      </c>
+      <c r="P55" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>5</v>
+      </c>
+      <c r="R55" s="3">
+        <v>5</v>
+      </c>
+      <c r="S55" s="3">
+        <v>5</v>
+      </c>
+      <c r="T55" s="3">
+        <v>0.28599999999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="18" thickBot="1">
+      <c r="A56" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" s="4">
+        <v>4</v>
+      </c>
+      <c r="E56" s="3">
+        <v>15</v>
+      </c>
+      <c r="F56" s="3">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K56" s="3">
+        <v>17</v>
+      </c>
+      <c r="L56" s="3">
+        <v>3</v>
+      </c>
+      <c r="M56" s="3">
+        <v>5</v>
+      </c>
+      <c r="N56" s="3">
+        <v>1</v>
+      </c>
+      <c r="O56" s="3">
+        <v>3</v>
+      </c>
+      <c r="P56" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="3">
+        <v>3</v>
+      </c>
+      <c r="R56" s="3">
+        <v>5</v>
+      </c>
+      <c r="S56" s="3">
+        <v>5</v>
+      </c>
+      <c r="T56" s="3">
+        <v>0.35699999999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" ht="18" thickBot="1">
+      <c r="A57" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" s="4">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6.14</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1</v>
+      </c>
+      <c r="G57" s="3">
+        <v>2</v>
+      </c>
+      <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K57" s="3">
+        <v>70</v>
+      </c>
+      <c r="L57" s="5">
+        <v>14.666666666666666</v>
+      </c>
+      <c r="M57" s="3">
+        <v>17</v>
+      </c>
+      <c r="N57" s="3">
+        <v>2</v>
+      </c>
+      <c r="O57" s="3">
+        <v>12</v>
+      </c>
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>12</v>
+      </c>
+      <c r="R57" s="3">
+        <v>11</v>
+      </c>
+      <c r="S57" s="3">
+        <v>10</v>
+      </c>
+      <c r="T57" s="3">
+        <v>0.30399999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" ht="18" thickBot="1">
+      <c r="A58" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="4">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3">
+        <v>7.71</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K58" s="3">
+        <v>14</v>
+      </c>
+      <c r="L58" s="5">
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="M58" s="3">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>2</v>
+      </c>
+      <c r="P58" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>2</v>
+      </c>
+      <c r="R58" s="3">
+        <v>2</v>
+      </c>
+      <c r="S58" s="3">
+        <v>2</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" ht="18" thickBot="1">
+      <c r="A59" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" s="4">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3.38</v>
+      </c>
+      <c r="F59" s="3">
+        <v>2</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1</v>
+      </c>
+      <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="K59" s="3">
+        <v>71</v>
+      </c>
+      <c r="L59" s="3">
+        <v>16</v>
+      </c>
+      <c r="M59" s="3">
+        <v>18</v>
+      </c>
+      <c r="N59" s="3">
+        <v>2</v>
+      </c>
+      <c r="O59" s="3">
+        <v>5</v>
+      </c>
+      <c r="P59" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>8</v>
+      </c>
+      <c r="R59" s="3">
+        <v>6</v>
+      </c>
+      <c r="S59" s="3">
+        <v>6</v>
+      </c>
+      <c r="T59" s="3">
+        <v>0.28100000000000003</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" ht="18" thickBot="1">
+      <c r="A60" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" s="4">
+        <v>2</v>
+      </c>
+      <c r="E60" s="3">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K60" s="3">
+        <v>12</v>
+      </c>
+      <c r="L60" s="5">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="M60" s="3">
+        <v>1</v>
+      </c>
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+      <c r="O60" s="3">
+        <v>1</v>
+      </c>
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>4</v>
+      </c>
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+      <c r="T60" s="3">
+        <v>9.0999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" ht="18" thickBot="1">
+      <c r="A61" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61" s="4">
+        <v>2</v>
+      </c>
+      <c r="E61" s="3">
+        <v>27</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
+        <v>1</v>
+      </c>
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
+        <v>18</v>
+      </c>
+      <c r="L61" s="5">
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="M61" s="3">
+        <v>7</v>
+      </c>
+      <c r="N61" s="3">
+        <v>1</v>
+      </c>
+      <c r="O61" s="3">
+        <v>2</v>
+      </c>
+      <c r="P61" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>8</v>
+      </c>
+      <c r="S61" s="3">
+        <v>8</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0.58299999999999996</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" ht="18" thickBot="1">
+      <c r="A62" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="4">
+        <v>2</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1.86</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>1</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
+        <v>40</v>
+      </c>
+      <c r="L62" s="5">
+        <v>9.6666666666666661</v>
+      </c>
+      <c r="M62" s="3">
+        <v>5</v>
+      </c>
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
+        <v>7</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>9</v>
+      </c>
+      <c r="R62" s="3">
+        <v>2</v>
+      </c>
+      <c r="S62" s="3">
+        <v>2</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" ht="18" thickBot="1">
+      <c r="A63" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="4">
+        <v>2</v>
+      </c>
+      <c r="E63" s="3">
+        <v>2.57</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0</v>
+      </c>
+      <c r="G63" s="3">
+        <v>1</v>
+      </c>
+      <c r="H63" s="3">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3">
+        <v>0</v>
+      </c>
+      <c r="K63" s="3">
+        <v>32</v>
+      </c>
+      <c r="L63" s="3">
+        <v>7</v>
+      </c>
+      <c r="M63" s="3">
+        <v>6</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>2</v>
+      </c>
+      <c r="P63" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>10</v>
+      </c>
+      <c r="R63" s="3">
+        <v>6</v>
+      </c>
+      <c r="S63" s="3">
+        <v>2</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0.214</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" ht="18" thickBot="1">
+      <c r="A64" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" s="4">
+        <v>2</v>
+      </c>
+      <c r="E64" s="3">
+        <v>10</v>
+      </c>
+      <c r="F64" s="3">
+        <v>0</v>
+      </c>
+      <c r="G64" s="3">
+        <v>1</v>
+      </c>
+      <c r="H64" s="3">
+        <v>0</v>
+      </c>
+      <c r="I64" s="3">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3">
+        <v>0</v>
+      </c>
+      <c r="K64" s="3">
+        <v>41</v>
+      </c>
+      <c r="L64" s="3">
+        <v>9</v>
+      </c>
+      <c r="M64" s="3">
+        <v>13</v>
+      </c>
+      <c r="N64" s="3">
+        <v>5</v>
+      </c>
+      <c r="O64" s="3">
+        <v>3</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>10</v>
+      </c>
+      <c r="R64" s="3">
+        <v>10</v>
+      </c>
+      <c r="S64" s="3">
+        <v>10</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0.34200000000000003</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" ht="18" thickBot="1">
+      <c r="A65" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D65" s="4">
+        <v>1</v>
+      </c>
+      <c r="E65" s="3">
+        <v>12</v>
+      </c>
+      <c r="F65" s="3">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3">
+        <v>1</v>
+      </c>
+      <c r="H65" s="3">
+        <v>0</v>
+      </c>
+      <c r="I65" s="3">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3">
+        <v>0</v>
+      </c>
+      <c r="K65" s="3">
+        <v>16</v>
+      </c>
+      <c r="L65" s="3">
+        <v>3</v>
+      </c>
+      <c r="M65" s="3">
+        <v>6</v>
+      </c>
+      <c r="N65" s="3">
+        <v>1</v>
+      </c>
+      <c r="O65" s="3">
+        <v>1</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>2</v>
+      </c>
+      <c r="R65" s="3">
+        <v>4</v>
+      </c>
+      <c r="S65" s="3">
+        <v>4</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" ht="18" thickBot="1">
+      <c r="A66" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D66" s="4">
+        <v>1</v>
+      </c>
+      <c r="E66" s="3">
+        <v>13.5</v>
+      </c>
+      <c r="F66" s="3">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K66" s="3">
+        <v>4</v>
+      </c>
+      <c r="L66" s="8">
+        <v>46056</v>
+      </c>
+      <c r="M66" s="3">
+        <v>2</v>
+      </c>
+      <c r="N66" s="3">
+        <v>0</v>
+      </c>
+      <c r="O66" s="3">
+        <v>0</v>
+      </c>
+      <c r="P66" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>0</v>
+      </c>
+      <c r="R66" s="3">
+        <v>1</v>
+      </c>
+      <c r="S66" s="3">
+        <v>1</v>
+      </c>
+      <c r="T66" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" ht="18" thickBot="1">
+      <c r="A67" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" s="4">
+        <v>1</v>
+      </c>
+      <c r="E67" s="3">
+        <v>11.25</v>
+      </c>
+      <c r="F67" s="3">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3">
+        <v>1</v>
+      </c>
+      <c r="H67" s="3">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3">
+        <v>0</v>
+      </c>
+      <c r="K67" s="3">
+        <v>20</v>
+      </c>
+      <c r="L67" s="3">
+        <v>4</v>
+      </c>
+      <c r="M67" s="3">
+        <v>6</v>
+      </c>
+      <c r="N67" s="3">
+        <v>2</v>
+      </c>
+      <c r="O67" s="3">
+        <v>2</v>
+      </c>
+      <c r="P67" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="3">
+        <v>2</v>
+      </c>
+      <c r="R67" s="3">
+        <v>5</v>
+      </c>
+      <c r="S67" s="3">
+        <v>5</v>
+      </c>
+      <c r="T67" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" ht="18" thickBot="1">
+      <c r="A68" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D68" s="4">
+        <v>1</v>
+      </c>
+      <c r="E68" s="3">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3">
+        <v>0</v>
+      </c>
+      <c r="I68" s="3">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K68" s="3">
+        <v>3</v>
+      </c>
+      <c r="L68" s="3">
+        <v>1</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>2</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" ht="18" thickBot="1">
+      <c r="A69" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69" s="4">
+        <v>1</v>
+      </c>
+      <c r="E69" s="3">
+        <v>4.91</v>
+      </c>
+      <c r="F69" s="3">
+        <v>0</v>
+      </c>
+      <c r="G69" s="3">
+        <v>0</v>
+      </c>
+      <c r="H69" s="3">
+        <v>0</v>
+      </c>
+      <c r="I69" s="3">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K69" s="3">
+        <v>20</v>
+      </c>
+      <c r="L69" s="5">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="M69" s="3">
+        <v>3</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>6</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>3</v>
+      </c>
+      <c r="R69" s="3">
+        <v>4</v>
+      </c>
+      <c r="S69" s="3">
+        <v>2</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0.214</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" ht="18" thickBot="1">
+      <c r="A70" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="4">
+        <v>1</v>
+      </c>
+      <c r="E70" s="3">
+        <v>6.75</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K70" s="3">
+        <v>8</v>
+      </c>
+      <c r="L70" s="5">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="M70" s="3">
+        <v>2</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>1</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>2</v>
+      </c>
+      <c r="R70" s="3">
+        <v>1</v>
+      </c>
+      <c r="S70" s="3">
+        <v>1</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0.28599999999999998</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" ht="18" thickBot="1">
+      <c r="A71" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" s="10">
+        <v>1</v>
+      </c>
+      <c r="E71" s="9">
+        <v>3.86</v>
+      </c>
+      <c r="F71" s="9">
+        <v>0</v>
+      </c>
+      <c r="G71" s="9">
+        <v>0</v>
+      </c>
+      <c r="H71" s="9">
+        <v>0</v>
+      </c>
+      <c r="I71" s="9">
+        <v>0</v>
+      </c>
+      <c r="J71" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K71" s="9">
+        <v>12</v>
+      </c>
+      <c r="L71" s="11">
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="M71" s="9">
+        <v>3</v>
+      </c>
+      <c r="N71" s="9">
+        <v>1</v>
+      </c>
+      <c r="O71" s="9">
+        <v>2</v>
+      </c>
+      <c r="P71" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="9">
+        <v>5</v>
+      </c>
+      <c r="R71" s="9">
+        <v>1</v>
+      </c>
+      <c r="S71" s="9">
+        <v>1</v>
+      </c>
+      <c r="T71" s="9">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" ht="18" thickBot="1">
+      <c r="A72" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q72" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R72" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S72" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T72" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" ht="18" thickBot="1">
+      <c r="A73" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D73" s="4">
+        <v>10</v>
+      </c>
+      <c r="E73" s="3">
+        <v>6.52</v>
+      </c>
+      <c r="F73" s="3">
+        <v>1</v>
+      </c>
+      <c r="G73" s="3">
+        <v>2</v>
+      </c>
+      <c r="H73" s="3">
+        <v>1</v>
+      </c>
+      <c r="I73" s="3">
+        <v>2</v>
+      </c>
+      <c r="J73" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K73" s="3">
+        <v>40</v>
+      </c>
+      <c r="L73" s="5">
+        <v>9.6666666666666661</v>
+      </c>
+      <c r="M73" s="3">
+        <v>4</v>
+      </c>
+      <c r="N73" s="3">
+        <v>1</v>
+      </c>
+      <c r="O73" s="3">
+        <v>6</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>4</v>
+      </c>
+      <c r="R73" s="3">
+        <v>7</v>
+      </c>
+      <c r="S73" s="3">
+        <v>7</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0.121</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" ht="18" thickBot="1">
+      <c r="A74" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" s="4">
+        <v>9</v>
+      </c>
+      <c r="E74" s="3">
+        <v>3.86</v>
+      </c>
+      <c r="F74" s="3">
+        <v>0</v>
+      </c>
+      <c r="G74" s="3">
+        <v>0</v>
+      </c>
+      <c r="H74" s="3">
+        <v>0</v>
+      </c>
+      <c r="I74" s="3">
+        <v>4</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K74" s="3">
+        <v>42</v>
+      </c>
+      <c r="L74" s="5">
+        <v>9.3333333333333339</v>
+      </c>
+      <c r="M74" s="3">
+        <v>10</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>5</v>
+      </c>
+      <c r="P74" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>12</v>
+      </c>
+      <c r="R74" s="3">
+        <v>4</v>
+      </c>
+      <c r="S74" s="3">
+        <v>4</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0.27800000000000002</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" ht="18" thickBot="1">
+      <c r="A75" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75" s="4">
+        <v>9</v>
+      </c>
+      <c r="E75" s="3">
+        <v>2.57</v>
+      </c>
+      <c r="F75" s="3">
+        <v>0</v>
+      </c>
+      <c r="G75" s="3">
+        <v>0</v>
+      </c>
+      <c r="H75" s="3">
+        <v>0</v>
+      </c>
+      <c r="I75" s="3">
+        <v>1</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K75" s="3">
+        <v>30</v>
+      </c>
+      <c r="L75" s="3">
+        <v>7</v>
+      </c>
+      <c r="M75" s="3">
+        <v>5</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>3</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>5</v>
+      </c>
+      <c r="R75" s="3">
+        <v>2</v>
+      </c>
+      <c r="S75" s="3">
+        <v>2</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0.185</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" ht="18" thickBot="1">
+      <c r="A76" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76" s="4">
+        <v>9</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4.66</v>
+      </c>
+      <c r="F76" s="3">
+        <v>1</v>
+      </c>
+      <c r="G76" s="3">
+        <v>1</v>
+      </c>
+      <c r="H76" s="3">
+        <v>3</v>
+      </c>
+      <c r="I76" s="3">
+        <v>1</v>
+      </c>
+      <c r="J76" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="K76" s="3">
+        <v>46</v>
+      </c>
+      <c r="L76" s="5">
+        <v>9.6666666666666661</v>
+      </c>
+      <c r="M76" s="3">
+        <v>12</v>
+      </c>
+      <c r="N76" s="3">
+        <v>0</v>
+      </c>
+      <c r="O76" s="3">
+        <v>5</v>
+      </c>
+      <c r="P76" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>12</v>
+      </c>
+      <c r="R76" s="3">
+        <v>7</v>
+      </c>
+      <c r="S76" s="3">
+        <v>5</v>
+      </c>
+      <c r="T76" s="3">
+        <v>0.32400000000000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" ht="18" thickBot="1">
+      <c r="A77" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D77" s="4">
+        <v>5</v>
+      </c>
+      <c r="E77" s="3">
+        <v>3</v>
+      </c>
+      <c r="F77" s="3">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3">
+        <v>0</v>
+      </c>
+      <c r="H77" s="3">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3">
+        <v>3</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K77" s="3">
+        <v>13</v>
+      </c>
+      <c r="L77" s="3">
+        <v>3</v>
+      </c>
+      <c r="M77" s="3">
+        <v>2</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>1</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>2</v>
+      </c>
+      <c r="R77" s="3">
+        <v>1</v>
+      </c>
+      <c r="S77" s="3">
+        <v>1</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0.182</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" ht="18" thickBot="1">
+      <c r="A78" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D78" s="4">
+        <v>5</v>
+      </c>
+      <c r="E78" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="F78" s="3">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3">
+        <v>0</v>
+      </c>
+      <c r="H78" s="3">
+        <v>0</v>
+      </c>
+      <c r="I78" s="3">
+        <v>1</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K78" s="3">
+        <v>9</v>
+      </c>
+      <c r="L78" s="5">
+        <v>1.6666666666666665</v>
+      </c>
+      <c r="M78" s="3">
+        <v>3</v>
+      </c>
+      <c r="N78" s="3">
+        <v>0</v>
+      </c>
+      <c r="O78" s="3">
+        <v>2</v>
+      </c>
+      <c r="P78" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="3">
+        <v>1</v>
+      </c>
+      <c r="R78" s="3">
+        <v>1</v>
+      </c>
+      <c r="S78" s="3">
+        <v>1</v>
+      </c>
+      <c r="T78" s="3">
+        <v>0.42899999999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" ht="18" thickBot="1">
+      <c r="A79" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D79" s="4">
+        <v>5</v>
+      </c>
+      <c r="E79" s="3">
+        <v>2.11</v>
+      </c>
+      <c r="F79" s="3">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3">
+        <v>0</v>
+      </c>
+      <c r="I79" s="3">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3">
+        <v>1</v>
+      </c>
+      <c r="K79" s="3">
+        <v>89</v>
+      </c>
+      <c r="L79" s="5">
+        <v>21.333333333333332</v>
+      </c>
+      <c r="M79" s="3">
+        <v>18</v>
+      </c>
+      <c r="N79" s="3">
+        <v>1</v>
+      </c>
+      <c r="O79" s="3">
+        <v>7</v>
+      </c>
+      <c r="P79" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q79" s="3">
+        <v>10</v>
+      </c>
+      <c r="R79" s="3">
+        <v>5</v>
+      </c>
+      <c r="S79" s="3">
+        <v>5</v>
+      </c>
+      <c r="T79" s="3">
+        <v>0.23100000000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" ht="18" thickBot="1">
+      <c r="A80" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D80" s="4">
+        <v>4</v>
+      </c>
+      <c r="E80" s="3">
+        <v>0</v>
+      </c>
+      <c r="F80" s="3">
+        <v>2</v>
+      </c>
+      <c r="G80" s="3">
+        <v>0</v>
+      </c>
+      <c r="H80" s="3">
+        <v>0</v>
+      </c>
+      <c r="I80" s="3">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3">
+        <v>1</v>
+      </c>
+      <c r="K80" s="3">
+        <v>20</v>
+      </c>
+      <c r="L80" s="5">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="M80" s="3">
+        <v>3</v>
+      </c>
+      <c r="N80" s="3">
+        <v>0</v>
+      </c>
+      <c r="O80" s="3">
+        <v>3</v>
+      </c>
+      <c r="P80" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="3">
+        <v>3</v>
+      </c>
+      <c r="R80" s="3">
+        <v>1</v>
+      </c>
+      <c r="S80" s="3">
+        <v>0</v>
+      </c>
+      <c r="T80" s="3">
+        <v>0.17599999999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" ht="18" thickBot="1">
+      <c r="A81" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D81" s="4">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2.35</v>
+      </c>
+      <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K81" s="3">
+        <v>64</v>
+      </c>
+      <c r="L81" s="5">
+        <v>15.333333333333334</v>
+      </c>
+      <c r="M81" s="3">
+        <v>16</v>
+      </c>
+      <c r="N81" s="3">
+        <v>1</v>
+      </c>
+      <c r="O81" s="3">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>16</v>
+      </c>
+      <c r="R81" s="3">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3">
+        <v>4</v>
+      </c>
+      <c r="T81" s="3">
+        <v>0.26200000000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" ht="18" thickBot="1">
+      <c r="A82" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D82" s="4">
+        <v>3</v>
+      </c>
+      <c r="E82" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="F82" s="3">
+        <v>3</v>
+      </c>
+      <c r="G82" s="3">
+        <v>0</v>
+      </c>
+      <c r="H82" s="3">
+        <v>0</v>
+      </c>
+      <c r="I82" s="3">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3">
+        <v>1</v>
+      </c>
+      <c r="K82" s="3">
+        <v>76</v>
+      </c>
+      <c r="L82" s="3">
+        <v>20</v>
+      </c>
+      <c r="M82" s="3">
+        <v>8</v>
+      </c>
+      <c r="N82" s="3">
+        <v>0</v>
+      </c>
+      <c r="O82" s="3">
+        <v>7</v>
+      </c>
+      <c r="P82" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q82" s="3">
+        <v>26</v>
+      </c>
+      <c r="R82" s="3">
+        <v>2</v>
+      </c>
+      <c r="S82" s="3">
+        <v>2</v>
+      </c>
+      <c r="T82" s="3">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" ht="18" thickBot="1">
+      <c r="A83" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D83" s="4">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1.42</v>
+      </c>
+      <c r="F83" s="3">
+        <v>1</v>
+      </c>
+      <c r="G83" s="3">
+        <v>1</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="K83" s="3">
+        <v>76</v>
+      </c>
+      <c r="L83" s="3">
+        <v>19</v>
+      </c>
+      <c r="M83" s="3">
+        <v>11</v>
+      </c>
+      <c r="N83" s="3">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
+        <v>4</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>13</v>
+      </c>
+      <c r="R83" s="3">
+        <v>4</v>
+      </c>
+      <c r="S83" s="3">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0.155</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" ht="18" thickBot="1">
+      <c r="A84" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D84" s="4">
+        <v>3</v>
+      </c>
+      <c r="E84" s="3">
+        <v>0</v>
+      </c>
+      <c r="F84" s="3">
+        <v>0</v>
+      </c>
+      <c r="G84" s="3">
+        <v>0</v>
+      </c>
+      <c r="H84" s="3">
+        <v>0</v>
+      </c>
+      <c r="I84" s="3">
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K84" s="3">
+        <v>13</v>
+      </c>
+      <c r="L84" s="5">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>3</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>3</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" ht="18" thickBot="1">
+      <c r="A85" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D85" s="4">
+        <v>2</v>
+      </c>
+      <c r="E85" s="3">
+        <v>9</v>
+      </c>
+      <c r="F85" s="3">
+        <v>1</v>
+      </c>
+      <c r="G85" s="3">
+        <v>0</v>
+      </c>
+      <c r="H85" s="3">
+        <v>0</v>
+      </c>
+      <c r="I85" s="3">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3">
+        <v>1</v>
+      </c>
+      <c r="K85" s="3">
+        <v>9</v>
+      </c>
+      <c r="L85" s="3">
+        <v>2</v>
+      </c>
+      <c r="M85" s="3">
+        <v>3</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>1</v>
+      </c>
+      <c r="R85" s="3">
+        <v>2</v>
+      </c>
+      <c r="S85" s="3">
+        <v>2</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" ht="18" thickBot="1">
+      <c r="A86" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" s="4">
+        <v>2</v>
+      </c>
+      <c r="E86" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="F86" s="3">
+        <v>1</v>
+      </c>
+      <c r="G86" s="3">
+        <v>1</v>
+      </c>
+      <c r="H86" s="3">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="K86" s="3">
+        <v>44</v>
+      </c>
+      <c r="L86" s="3">
+        <v>10</v>
+      </c>
+      <c r="M86" s="3">
+        <v>13</v>
+      </c>
+      <c r="N86" s="3">
+        <v>1</v>
+      </c>
+      <c r="O86" s="3">
+        <v>2</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>7</v>
+      </c>
+      <c r="R86" s="3">
+        <v>7</v>
+      </c>
+      <c r="S86" s="3">
+        <v>6</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" ht="18" thickBot="1">
+      <c r="A87" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D87" s="4">
+        <v>1</v>
+      </c>
+      <c r="E87" s="3">
+        <v>27</v>
+      </c>
+      <c r="F87" s="3">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3">
+        <v>0</v>
+      </c>
+      <c r="I87" s="3">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K87" s="3">
+        <v>5</v>
+      </c>
+      <c r="L87" s="8">
+        <v>46025</v>
+      </c>
+      <c r="M87" s="3">
+        <v>2</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>2</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>1</v>
+      </c>
+      <c r="S87" s="3">
+        <v>1</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0.66700000000000004</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" ht="18" thickBot="1">
+      <c r="A88" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D88" s="4">
+        <v>1</v>
+      </c>
+      <c r="E88" s="3">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3">
+        <v>0</v>
+      </c>
+      <c r="H88" s="3">
+        <v>0</v>
+      </c>
+      <c r="I88" s="3">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K88" s="3">
+        <v>4</v>
+      </c>
+      <c r="L88" s="3">
+        <v>1</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>1</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" ht="18" thickBot="1">
+      <c r="A89" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D89" s="4">
+        <v>1</v>
+      </c>
+      <c r="E89" s="3">
+        <v>7.71</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K89" s="3">
+        <v>13</v>
+      </c>
+      <c r="L89" s="5">
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="M89" s="3">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
+        <v>1</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
+        <v>2</v>
+      </c>
+      <c r="S89" s="3">
+        <v>2</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0.41699999999999998</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" ht="18" thickBot="1">
+      <c r="A90" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D90" s="4">
+        <v>1</v>
+      </c>
+      <c r="E90" s="3">
+        <v>13.5</v>
+      </c>
+      <c r="F90" s="3">
+        <v>0</v>
+      </c>
+      <c r="G90" s="3">
+        <v>0</v>
+      </c>
+      <c r="H90" s="3">
+        <v>0</v>
+      </c>
+      <c r="I90" s="3">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K90" s="3">
+        <v>4</v>
+      </c>
+      <c r="L90" s="8">
+        <v>46056</v>
+      </c>
+      <c r="M90" s="3">
+        <v>2</v>
+      </c>
+      <c r="N90" s="3">
+        <v>0</v>
+      </c>
+      <c r="O90" s="3">
+        <v>0</v>
+      </c>
+      <c r="P90" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="3">
+        <v>1</v>
+      </c>
+      <c r="R90" s="3">
+        <v>1</v>
+      </c>
+      <c r="S90" s="3">
+        <v>1</v>
+      </c>
+      <c r="T90" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" ht="18" thickBot="1">
+      <c r="A91" s="3">
+        <v>2023</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D91" s="10">
+        <v>1</v>
+      </c>
+      <c r="E91" s="9">
+        <v>7.36</v>
+      </c>
+      <c r="F91" s="9">
+        <v>0</v>
+      </c>
+      <c r="G91" s="9">
+        <v>0</v>
+      </c>
+      <c r="H91" s="9">
+        <v>0</v>
+      </c>
+      <c r="I91" s="9">
+        <v>0</v>
+      </c>
+      <c r="J91" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K91" s="9">
+        <v>18</v>
+      </c>
+      <c r="L91" s="11">
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="M91" s="9">
+        <v>5</v>
+      </c>
+      <c r="N91" s="9">
+        <v>1</v>
+      </c>
+      <c r="O91" s="9">
+        <v>1</v>
+      </c>
+      <c r="P91" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q91" s="9">
+        <v>3</v>
+      </c>
+      <c r="R91" s="9">
+        <v>3</v>
+      </c>
+      <c r="S91" s="9">
+        <v>3</v>
+      </c>
+      <c r="T91" s="9">
+        <v>0.35699999999999998</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" ht="18" thickBot="1">
+      <c r="A92" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N92" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O92" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P92" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q92" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R92" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S92" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T92" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" ht="18" thickBot="1">
+      <c r="A93" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D93" s="4">
+        <v>8</v>
+      </c>
+      <c r="E93" s="3">
+        <v>4.32</v>
+      </c>
+      <c r="F93" s="3">
+        <v>0</v>
+      </c>
+      <c r="G93" s="3">
+        <v>0</v>
+      </c>
+      <c r="H93" s="3">
+        <v>0</v>
+      </c>
+      <c r="I93" s="3">
+        <v>2</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K93" s="3">
+        <v>37</v>
+      </c>
+      <c r="L93" s="5">
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="M93" s="3">
+        <v>8</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>4</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>12</v>
+      </c>
+      <c r="R93" s="3">
+        <v>4</v>
+      </c>
+      <c r="S93" s="3">
+        <v>4</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" ht="18" thickBot="1">
+      <c r="A94" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D94" s="4">
+        <v>6</v>
+      </c>
+      <c r="E94" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="F94" s="3">
+        <v>2</v>
+      </c>
+      <c r="G94" s="3">
+        <v>1</v>
+      </c>
+      <c r="H94" s="3">
+        <v>2</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="K94" s="3">
+        <v>25</v>
+      </c>
+      <c r="L94" s="5">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="M94" s="3">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
+        <v>1</v>
+      </c>
+      <c r="O94" s="3">
+        <v>1</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3">
+        <v>2</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0.13600000000000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" ht="18" thickBot="1">
+      <c r="A95" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D95" s="4">
+        <v>5</v>
+      </c>
+      <c r="E95" s="3">
+        <v>1.17</v>
+      </c>
+      <c r="F95" s="3">
+        <v>1</v>
+      </c>
+      <c r="G95" s="3">
+        <v>0</v>
+      </c>
+      <c r="H95" s="3">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3">
+        <v>1</v>
+      </c>
+      <c r="K95" s="3">
+        <v>26</v>
+      </c>
+      <c r="L95" s="5">
+        <v>7.666666666666667</v>
+      </c>
+      <c r="M95" s="3">
+        <v>3</v>
+      </c>
+      <c r="N95" s="3">
+        <v>0</v>
+      </c>
+      <c r="O95" s="3">
+        <v>2</v>
+      </c>
+      <c r="P95" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="3">
+        <v>3</v>
+      </c>
+      <c r="R95" s="3">
+        <v>1</v>
+      </c>
+      <c r="S95" s="3">
+        <v>1</v>
+      </c>
+      <c r="T95" s="3">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" ht="18" thickBot="1">
+      <c r="A96" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D96" s="4">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3">
+        <v>4.13</v>
+      </c>
+      <c r="F96" s="3">
+        <v>1</v>
+      </c>
+      <c r="G96" s="3">
+        <v>2</v>
+      </c>
+      <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K96" s="3">
+        <v>106</v>
+      </c>
+      <c r="L96" s="3">
+        <v>24</v>
+      </c>
+      <c r="M96" s="3">
+        <v>24</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>9</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>13</v>
+      </c>
+      <c r="R96" s="3">
+        <v>15</v>
+      </c>
+      <c r="S96" s="3">
+        <v>11</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0.255</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" ht="18" thickBot="1">
+      <c r="A97" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D97" s="4">
+        <v>4</v>
+      </c>
+      <c r="E97" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="F97" s="3">
+        <v>0</v>
+      </c>
+      <c r="G97" s="3">
+        <v>1</v>
+      </c>
+      <c r="H97" s="3">
+        <v>1</v>
+      </c>
+      <c r="I97" s="3">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3">
+        <v>0</v>
+      </c>
+      <c r="K97" s="3">
+        <v>19</v>
+      </c>
+      <c r="L97" s="5">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="M97" s="3">
+        <v>6</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>3</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>1</v>
+      </c>
+      <c r="R97" s="3">
+        <v>4</v>
+      </c>
+      <c r="S97" s="3">
+        <v>3</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0.42899999999999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" ht="18" thickBot="1">
+      <c r="A98" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D98" s="4">
+        <v>4</v>
+      </c>
+      <c r="E98" s="3">
+        <v>9</v>
+      </c>
+      <c r="F98" s="3">
+        <v>0</v>
+      </c>
+      <c r="G98" s="3">
+        <v>0</v>
+      </c>
+      <c r="H98" s="3">
+        <v>0</v>
+      </c>
+      <c r="I98" s="3">
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K98" s="3">
+        <v>20</v>
+      </c>
+      <c r="L98" s="3">
+        <v>4</v>
+      </c>
+      <c r="M98" s="3">
+        <v>8</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>1</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>4</v>
+      </c>
+      <c r="R98" s="3">
+        <v>4</v>
+      </c>
+      <c r="S98" s="3">
+        <v>4</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0.42099999999999999</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" ht="18" thickBot="1">
+      <c r="A99" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D99" s="4">
+        <v>4</v>
+      </c>
+      <c r="E99" s="3">
+        <v>7.36</v>
+      </c>
+      <c r="F99" s="3">
+        <v>0</v>
+      </c>
+      <c r="G99" s="3">
+        <v>0</v>
+      </c>
+      <c r="H99" s="3">
+        <v>0</v>
+      </c>
+      <c r="I99" s="3">
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K99" s="3">
+        <v>39</v>
+      </c>
+      <c r="L99" s="5">
+        <v>7.333333333333333</v>
+      </c>
+      <c r="M99" s="3">
+        <v>12</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>4</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>7</v>
+      </c>
+      <c r="R99" s="3">
+        <v>6</v>
+      </c>
+      <c r="S99" s="3">
+        <v>6</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0.35299999999999998</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20" ht="18" thickBot="1">
+      <c r="A100" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D100" s="4">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2.08</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K100" s="3">
+        <v>21</v>
+      </c>
+      <c r="L100" s="5">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="M100" s="3">
+        <v>6</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>1</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>1</v>
+      </c>
+      <c r="R100" s="3">
+        <v>1</v>
+      </c>
+      <c r="S100" s="3">
+        <v>1</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" ht="18" thickBot="1">
+      <c r="A101" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D101" s="4">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3">
+        <v>7.94</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>1</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>1</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>27</v>
+      </c>
+      <c r="L101" s="5">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="M101" s="3">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>1</v>
+      </c>
+      <c r="R101" s="3">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0.34799999999999998</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20" ht="18" thickBot="1">
+      <c r="A102" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D102" s="4">
+        <v>4</v>
+      </c>
+      <c r="E102" s="3">
+        <v>6.48</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>1</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K102" s="3">
+        <v>40</v>
+      </c>
+      <c r="L102" s="5">
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="M102" s="3">
+        <v>15</v>
+      </c>
+      <c r="N102" s="3">
+        <v>2</v>
+      </c>
+      <c r="O102" s="3">
+        <v>1</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>7</v>
+      </c>
+      <c r="R102" s="3">
+        <v>7</v>
+      </c>
+      <c r="S102" s="3">
+        <v>6</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0.38500000000000001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20" ht="18" thickBot="1">
+      <c r="A103" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D103" s="4">
+        <v>4</v>
+      </c>
+      <c r="E103" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="F103" s="3">
+        <v>1</v>
+      </c>
+      <c r="G103" s="3">
+        <v>2</v>
+      </c>
+      <c r="H103" s="3">
+        <v>0</v>
+      </c>
+      <c r="I103" s="3">
+        <v>0</v>
+      </c>
+      <c r="J103" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="K103" s="3">
+        <v>93</v>
+      </c>
+      <c r="L103" s="3">
+        <v>20</v>
+      </c>
+      <c r="M103" s="3">
+        <v>30</v>
+      </c>
+      <c r="N103" s="3">
+        <v>3</v>
+      </c>
+      <c r="O103" s="3">
+        <v>1</v>
+      </c>
+      <c r="P103" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q103" s="3">
+        <v>11</v>
+      </c>
+      <c r="R103" s="3">
+        <v>12</v>
+      </c>
+      <c r="S103" s="3">
+        <v>12</v>
+      </c>
+      <c r="T103" s="3">
+        <v>0.34899999999999998</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20" ht="18" thickBot="1">
+      <c r="A104" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D104" s="4">
+        <v>3</v>
+      </c>
+      <c r="E104" s="3">
+        <v>6.35</v>
+      </c>
+      <c r="F104" s="3">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3">
+        <v>2</v>
+      </c>
+      <c r="H104" s="3">
+        <v>0</v>
+      </c>
+      <c r="I104" s="3">
+        <v>0</v>
+      </c>
+      <c r="J104" s="3">
+        <v>0</v>
+      </c>
+      <c r="K104" s="3">
+        <v>82</v>
+      </c>
+      <c r="L104" s="3">
+        <v>17</v>
+      </c>
+      <c r="M104" s="3">
+        <v>25</v>
+      </c>
+      <c r="N104" s="3">
+        <v>3</v>
+      </c>
+      <c r="O104" s="3">
+        <v>6</v>
+      </c>
+      <c r="P104" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="3">
+        <v>14</v>
+      </c>
+      <c r="R104" s="3">
+        <v>17</v>
+      </c>
+      <c r="S104" s="3">
+        <v>12</v>
+      </c>
+      <c r="T104" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+    </row>
+    <row r="105" spans="1:20" ht="18" thickBot="1">
+      <c r="A105" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D105" s="4">
+        <v>3</v>
+      </c>
+      <c r="E105" s="3">
+        <v>6.75</v>
+      </c>
+      <c r="F105" s="3">
+        <v>0</v>
+      </c>
+      <c r="G105" s="3">
+        <v>0</v>
+      </c>
+      <c r="H105" s="3">
+        <v>0</v>
+      </c>
+      <c r="I105" s="3">
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K105" s="3">
+        <v>19</v>
+      </c>
+      <c r="L105" s="3">
+        <v>4</v>
+      </c>
+      <c r="M105" s="3">
+        <v>7</v>
+      </c>
+      <c r="N105" s="3">
+        <v>2</v>
+      </c>
+      <c r="O105" s="3">
+        <v>0</v>
+      </c>
+      <c r="P105" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="3">
+        <v>0</v>
+      </c>
+      <c r="R105" s="3">
+        <v>4</v>
+      </c>
+      <c r="S105" s="3">
+        <v>3</v>
+      </c>
+      <c r="T105" s="3">
+        <v>0.38900000000000001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:20" ht="18" thickBot="1">
+      <c r="A106" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D106" s="4">
+        <v>3</v>
+      </c>
+      <c r="E106" s="3">
+        <v>0</v>
+      </c>
+      <c r="F106" s="3">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3">
+        <v>0</v>
+      </c>
+      <c r="H106" s="3">
+        <v>0</v>
+      </c>
+      <c r="I106" s="3">
+        <v>0</v>
+      </c>
+      <c r="J106" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K106" s="3">
+        <v>7</v>
+      </c>
+      <c r="L106" s="3">
+        <v>1</v>
+      </c>
+      <c r="M106" s="3">
+        <v>0</v>
+      </c>
+      <c r="N106" s="3">
+        <v>0</v>
+      </c>
+      <c r="O106" s="3">
+        <v>4</v>
+      </c>
+      <c r="P106" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="3">
+        <v>1</v>
+      </c>
+      <c r="R106" s="3">
+        <v>0</v>
+      </c>
+      <c r="S106" s="3">
+        <v>0</v>
+      </c>
+      <c r="T106" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20" ht="18" thickBot="1">
+      <c r="A107" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D107" s="4">
+        <v>3</v>
+      </c>
+      <c r="E107" s="3">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="F107" s="3">
+        <v>0</v>
+      </c>
+      <c r="G107" s="3">
+        <v>2</v>
+      </c>
+      <c r="H107" s="3">
+        <v>0</v>
+      </c>
+      <c r="I107" s="3">
+        <v>0</v>
+      </c>
+      <c r="J107" s="3">
+        <v>0</v>
+      </c>
+      <c r="K107" s="3">
+        <v>59</v>
+      </c>
+      <c r="L107" s="5">
+        <v>10.666666666666666</v>
+      </c>
+      <c r="M107" s="3">
+        <v>12</v>
+      </c>
+      <c r="N107" s="3">
+        <v>0</v>
+      </c>
+      <c r="O107" s="3">
+        <v>12</v>
+      </c>
+      <c r="P107" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q107" s="3">
+        <v>7</v>
+      </c>
+      <c r="R107" s="3">
+        <v>12</v>
+      </c>
+      <c r="S107" s="3">
+        <v>11</v>
+      </c>
+      <c r="T107" s="3">
+        <v>0.32400000000000001</v>
+      </c>
+    </row>
+    <row r="108" spans="1:20" ht="18" thickBot="1">
+      <c r="A108" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D108" s="4">
+        <v>2</v>
+      </c>
+      <c r="E108" s="3">
+        <v>9</v>
+      </c>
+      <c r="F108" s="3">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3">
+        <v>0</v>
+      </c>
+      <c r="H108" s="3">
+        <v>0</v>
+      </c>
+      <c r="I108" s="3">
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K108" s="3">
+        <v>10</v>
+      </c>
+      <c r="L108" s="3">
+        <v>1</v>
+      </c>
+      <c r="M108" s="3">
+        <v>3</v>
+      </c>
+      <c r="N108" s="3">
+        <v>0</v>
+      </c>
+      <c r="O108" s="3">
+        <v>1</v>
+      </c>
+      <c r="P108" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q108" s="3">
+        <v>1</v>
+      </c>
+      <c r="R108" s="3">
+        <v>3</v>
+      </c>
+      <c r="S108" s="3">
+        <v>1</v>
+      </c>
+      <c r="T108" s="3">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="109" spans="1:20" ht="18" thickBot="1">
+      <c r="A109" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D109" s="4">
+        <v>2</v>
+      </c>
+      <c r="E109" s="3">
+        <v>27</v>
+      </c>
+      <c r="F109" s="3">
+        <v>0</v>
+      </c>
+      <c r="G109" s="3">
+        <v>0</v>
+      </c>
+      <c r="H109" s="3">
+        <v>0</v>
+      </c>
+      <c r="I109" s="3">
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K109" s="3">
+        <v>14</v>
+      </c>
+      <c r="L109" s="3">
+        <v>2</v>
+      </c>
+      <c r="M109" s="3">
+        <v>6</v>
+      </c>
+      <c r="N109" s="3">
+        <v>0</v>
+      </c>
+      <c r="O109" s="3">
+        <v>2</v>
+      </c>
+      <c r="P109" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="3">
+        <v>2</v>
+      </c>
+      <c r="R109" s="3">
+        <v>6</v>
+      </c>
+      <c r="S109" s="3">
+        <v>6</v>
+      </c>
+      <c r="T109" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:20" ht="18" thickBot="1">
+      <c r="A110" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D110" s="4">
+        <v>1</v>
+      </c>
+      <c r="E110" s="3">
+        <v>9</v>
+      </c>
+      <c r="F110" s="3">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3">
+        <v>0</v>
+      </c>
+      <c r="H110" s="3">
+        <v>0</v>
+      </c>
+      <c r="I110" s="3">
+        <v>0</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K110" s="3">
+        <v>10</v>
+      </c>
+      <c r="L110" s="3">
+        <v>2</v>
+      </c>
+      <c r="M110" s="3">
+        <v>3</v>
+      </c>
+      <c r="N110" s="3">
+        <v>0</v>
+      </c>
+      <c r="O110" s="3">
+        <v>1</v>
+      </c>
+      <c r="P110" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="3">
+        <v>0</v>
+      </c>
+      <c r="R110" s="3">
+        <v>2</v>
+      </c>
+      <c r="S110" s="3">
+        <v>2</v>
+      </c>
+      <c r="T110" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+    </row>
+    <row r="111" spans="1:20" ht="18" thickBot="1">
+      <c r="A111" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D111" s="4">
+        <v>1</v>
+      </c>
+      <c r="E111" s="3">
+        <v>27</v>
+      </c>
+      <c r="F111" s="3">
+        <v>0</v>
+      </c>
+      <c r="G111" s="3">
+        <v>0</v>
+      </c>
+      <c r="H111" s="3">
+        <v>0</v>
+      </c>
+      <c r="I111" s="3">
+        <v>0</v>
+      </c>
+      <c r="J111" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K111" s="3">
+        <v>5</v>
+      </c>
+      <c r="L111" s="8">
+        <v>46025</v>
+      </c>
+      <c r="M111" s="3">
+        <v>3</v>
+      </c>
+      <c r="N111" s="3">
+        <v>0</v>
+      </c>
+      <c r="O111" s="3">
+        <v>1</v>
+      </c>
+      <c r="P111" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="3">
+        <v>0</v>
+      </c>
+      <c r="R111" s="3">
+        <v>1</v>
+      </c>
+      <c r="S111" s="3">
+        <v>1</v>
+      </c>
+      <c r="T111" s="3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="112" spans="1:20" ht="18" thickBot="1">
+      <c r="A112" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D112" s="4">
+        <v>1</v>
+      </c>
+      <c r="E112" s="3">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3">
+        <v>0</v>
+      </c>
+      <c r="H112" s="3">
+        <v>0</v>
+      </c>
+      <c r="I112" s="3">
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K112" s="3">
+        <v>2</v>
+      </c>
+      <c r="L112" s="8">
+        <v>46025</v>
+      </c>
+      <c r="M112" s="3">
+        <v>0</v>
+      </c>
+      <c r="N112" s="3">
+        <v>0</v>
+      </c>
+      <c r="O112" s="3">
+        <v>1</v>
+      </c>
+      <c r="P112" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="3">
+        <v>0</v>
+      </c>
+      <c r="R112" s="3">
+        <v>0</v>
+      </c>
+      <c r="S112" s="3">
+        <v>0</v>
+      </c>
+      <c r="T112" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20" ht="18" thickBot="1">
+      <c r="A113" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D113" s="4">
+        <v>1</v>
+      </c>
+      <c r="E113" s="3">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3">
+        <v>0</v>
+      </c>
+      <c r="G113" s="3">
+        <v>0</v>
+      </c>
+      <c r="H113" s="3">
+        <v>0</v>
+      </c>
+      <c r="I113" s="3">
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K113" s="3">
+        <v>1</v>
+      </c>
+      <c r="L113" s="8">
+        <v>46025</v>
+      </c>
+      <c r="M113" s="3">
+        <v>0</v>
+      </c>
+      <c r="N113" s="3">
+        <v>0</v>
+      </c>
+      <c r="O113" s="3">
+        <v>0</v>
+      </c>
+      <c r="P113" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="3">
+        <v>0</v>
+      </c>
+      <c r="R113" s="3">
+        <v>0</v>
+      </c>
+      <c r="S113" s="3">
+        <v>0</v>
+      </c>
+      <c r="T113" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20" ht="18" thickBot="1">
+      <c r="A114" s="3">
+        <v>2022</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D114" s="10">
+        <v>1</v>
+      </c>
+      <c r="E114" s="9">
+        <v>0</v>
+      </c>
+      <c r="F114" s="9">
+        <v>0</v>
+      </c>
+      <c r="G114" s="9">
+        <v>0</v>
+      </c>
+      <c r="H114" s="9">
+        <v>0</v>
+      </c>
+      <c r="I114" s="9">
+        <v>1</v>
+      </c>
+      <c r="J114" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K114" s="9">
+        <v>1</v>
+      </c>
+      <c r="L114" s="12">
+        <v>46025</v>
+      </c>
+      <c r="M114" s="9">
+        <v>0</v>
+      </c>
+      <c r="N114" s="9">
+        <v>0</v>
+      </c>
+      <c r="O114" s="9">
+        <v>0</v>
+      </c>
+      <c r="P114" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="9">
+        <v>1</v>
+      </c>
+      <c r="R114" s="9">
+        <v>0</v>
+      </c>
+      <c r="S114" s="9">
+        <v>0</v>
+      </c>
+      <c r="T114" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20" ht="18" thickBot="1">
+      <c r="A115" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L115" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N115" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O115" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P115" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q115" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R115" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S115" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T115" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20" ht="18" thickBot="1">
+      <c r="A116" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D116" s="4">
+        <v>7</v>
+      </c>
+      <c r="E116" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="F116" s="3">
+        <v>1</v>
+      </c>
+      <c r="G116" s="3">
+        <v>0</v>
+      </c>
+      <c r="H116" s="3">
+        <v>0</v>
+      </c>
+      <c r="I116" s="3">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3">
+        <v>1</v>
+      </c>
+      <c r="K116" s="3">
+        <v>49</v>
+      </c>
+      <c r="L116" s="5">
+        <v>10.333333333333334</v>
+      </c>
+      <c r="M116" s="3">
+        <v>17</v>
+      </c>
+      <c r="N116" s="3">
+        <v>1</v>
+      </c>
+      <c r="O116" s="3">
+        <v>0</v>
+      </c>
+      <c r="P116" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="3">
+        <v>5</v>
+      </c>
+      <c r="R116" s="3">
+        <v>8</v>
+      </c>
+      <c r="S116" s="3">
+        <v>7</v>
+      </c>
+      <c r="T116" s="3">
+        <v>0.35399999999999998</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20" ht="18" thickBot="1">
+      <c r="A117" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D117" s="4">
+        <v>6</v>
+      </c>
+      <c r="E117" s="3">
+        <v>2.84</v>
+      </c>
+      <c r="F117" s="3">
+        <v>0</v>
+      </c>
+      <c r="G117" s="3">
+        <v>0</v>
+      </c>
+      <c r="H117" s="3">
+        <v>4</v>
+      </c>
+      <c r="I117" s="3">
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K117" s="3">
+        <v>26</v>
+      </c>
+      <c r="L117" s="5">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="M117" s="3">
+        <v>6</v>
+      </c>
+      <c r="N117" s="3">
+        <v>0</v>
+      </c>
+      <c r="O117" s="3">
+        <v>2</v>
+      </c>
+      <c r="P117" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q117" s="3">
+        <v>5</v>
+      </c>
+      <c r="R117" s="3">
+        <v>3</v>
+      </c>
+      <c r="S117" s="3">
+        <v>2</v>
+      </c>
+      <c r="T117" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="118" spans="1:20" ht="18" thickBot="1">
+      <c r="A118" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D118" s="4">
+        <v>6</v>
+      </c>
+      <c r="E118" s="3">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="F118" s="3">
+        <v>0</v>
+      </c>
+      <c r="G118" s="3">
+        <v>0</v>
+      </c>
+      <c r="H118" s="3">
+        <v>0</v>
+      </c>
+      <c r="I118" s="3">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K118" s="3">
+        <v>30</v>
+      </c>
+      <c r="L118" s="5">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="M118" s="3">
+        <v>10</v>
+      </c>
+      <c r="N118" s="3">
+        <v>0</v>
+      </c>
+      <c r="O118" s="3">
+        <v>2</v>
+      </c>
+      <c r="P118" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q118" s="3">
+        <v>5</v>
+      </c>
+      <c r="R118" s="3">
+        <v>6</v>
+      </c>
+      <c r="S118" s="3">
+        <v>6</v>
+      </c>
+      <c r="T118" s="3">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20" ht="18" thickBot="1">
+      <c r="A119" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D119" s="4">
+        <v>6</v>
+      </c>
+      <c r="E119" s="3">
+        <v>1.35</v>
+      </c>
+      <c r="F119" s="3">
+        <v>2</v>
+      </c>
+      <c r="G119" s="3">
+        <v>0</v>
+      </c>
+      <c r="H119" s="3">
+        <v>0</v>
+      </c>
+      <c r="I119" s="3">
+        <v>3</v>
+      </c>
+      <c r="J119" s="3">
+        <v>1</v>
+      </c>
+      <c r="K119" s="3">
+        <v>26</v>
+      </c>
+      <c r="L119" s="5">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="M119" s="3">
+        <v>8</v>
+      </c>
+      <c r="N119" s="3">
+        <v>0</v>
+      </c>
+      <c r="O119" s="3">
+        <v>0</v>
+      </c>
+      <c r="P119" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="3">
+        <v>1</v>
+      </c>
+      <c r="R119" s="3">
+        <v>1</v>
+      </c>
+      <c r="S119" s="3">
+        <v>1</v>
+      </c>
+      <c r="T119" s="3">
+        <v>0.308</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20" ht="18" thickBot="1">
+      <c r="A120" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D120" s="4">
+        <v>5</v>
+      </c>
+      <c r="E120" s="3">
+        <v>1.59</v>
+      </c>
+      <c r="F120" s="3">
+        <v>0</v>
+      </c>
+      <c r="G120" s="3">
+        <v>0</v>
+      </c>
+      <c r="H120" s="3">
+        <v>0</v>
+      </c>
+      <c r="I120" s="3">
+        <v>3</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K120" s="3">
+        <v>22</v>
+      </c>
+      <c r="L120" s="5">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="M120" s="3">
+        <v>6</v>
+      </c>
+      <c r="N120" s="3">
+        <v>0</v>
+      </c>
+      <c r="O120" s="3">
+        <v>1</v>
+      </c>
+      <c r="P120" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="3">
+        <v>5</v>
+      </c>
+      <c r="R120" s="3">
+        <v>1</v>
+      </c>
+      <c r="S120" s="3">
+        <v>1</v>
+      </c>
+      <c r="T120" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:20" ht="18" thickBot="1">
+      <c r="A121" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" s="4">
+        <v>4</v>
+      </c>
+      <c r="E121" s="3">
+        <v>21.94</v>
+      </c>
+      <c r="F121" s="3">
+        <v>0</v>
+      </c>
+      <c r="G121" s="3">
+        <v>0</v>
+      </c>
+      <c r="H121" s="3">
+        <v>0</v>
+      </c>
+      <c r="I121" s="3">
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K121" s="3">
+        <v>33</v>
+      </c>
+      <c r="L121" s="5">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="M121" s="3">
+        <v>14</v>
+      </c>
+      <c r="N121" s="3">
+        <v>3</v>
+      </c>
+      <c r="O121" s="3">
+        <v>4</v>
+      </c>
+      <c r="P121" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="3">
+        <v>2</v>
+      </c>
+      <c r="R121" s="3">
+        <v>13</v>
+      </c>
+      <c r="S121" s="3">
+        <v>13</v>
+      </c>
+      <c r="T121" s="3">
+        <v>0.51900000000000002</v>
+      </c>
+    </row>
+    <row r="122" spans="1:20" ht="18" thickBot="1">
+      <c r="A122" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D122" s="4">
+        <v>4</v>
+      </c>
+      <c r="E122" s="3">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3">
+        <v>0</v>
+      </c>
+      <c r="H122" s="3">
+        <v>0</v>
+      </c>
+      <c r="I122" s="3">
+        <v>2</v>
+      </c>
+      <c r="J122" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K122" s="3">
+        <v>13</v>
+      </c>
+      <c r="L122" s="5">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="M122" s="3">
+        <v>2</v>
+      </c>
+      <c r="N122" s="3">
+        <v>0</v>
+      </c>
+      <c r="O122" s="3">
+        <v>1</v>
+      </c>
+      <c r="P122" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="3">
+        <v>0</v>
+      </c>
+      <c r="R122" s="3">
+        <v>0</v>
+      </c>
+      <c r="S122" s="3">
+        <v>0</v>
+      </c>
+      <c r="T122" s="3">
+        <v>0.16700000000000001</v>
+      </c>
+    </row>
+    <row r="123" spans="1:20" ht="18" thickBot="1">
+      <c r="A123" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D123" s="4">
+        <v>4</v>
+      </c>
+      <c r="E123" s="3">
+        <v>5.71</v>
+      </c>
+      <c r="F123" s="3">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3">
+        <v>2</v>
+      </c>
+      <c r="H123" s="3">
+        <v>0</v>
+      </c>
+      <c r="I123" s="3">
+        <v>0</v>
+      </c>
+      <c r="J123" s="3">
+        <v>0</v>
+      </c>
+      <c r="K123" s="3">
+        <v>80</v>
+      </c>
+      <c r="L123" s="5">
+        <v>17.333333333333332</v>
+      </c>
+      <c r="M123" s="3">
+        <v>19</v>
+      </c>
+      <c r="N123" s="3">
+        <v>3</v>
+      </c>
+      <c r="O123" s="3">
+        <v>11</v>
+      </c>
+      <c r="P123" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q123" s="3">
+        <v>8</v>
+      </c>
+      <c r="R123" s="3">
+        <v>14</v>
+      </c>
+      <c r="S123" s="3">
+        <v>11</v>
+      </c>
+      <c r="T123" s="3">
+        <v>0.28399999999999997</v>
+      </c>
+    </row>
+    <row r="124" spans="1:20" ht="18" thickBot="1">
+      <c r="A124" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D124" s="4">
+        <v>4</v>
+      </c>
+      <c r="E124" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="F124" s="3">
+        <v>0</v>
+      </c>
+      <c r="G124" s="3">
+        <v>0</v>
+      </c>
+      <c r="H124" s="3">
+        <v>1</v>
+      </c>
+      <c r="I124" s="3">
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K124" s="3">
+        <v>13</v>
+      </c>
+      <c r="L124" s="5">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="M124" s="3">
+        <v>2</v>
+      </c>
+      <c r="N124" s="3">
+        <v>0</v>
+      </c>
+      <c r="O124" s="3">
+        <v>1</v>
+      </c>
+      <c r="P124" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="3">
+        <v>1</v>
+      </c>
+      <c r="R124" s="3">
+        <v>2</v>
+      </c>
+      <c r="S124" s="3">
+        <v>2</v>
+      </c>
+      <c r="T124" s="3">
+        <v>0.182</v>
+      </c>
+    </row>
+    <row r="125" spans="1:20" ht="18" thickBot="1">
+      <c r="A125" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D125" s="4">
+        <v>4</v>
+      </c>
+      <c r="E125" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="F125" s="3">
+        <v>3</v>
+      </c>
+      <c r="G125" s="3">
+        <v>0</v>
+      </c>
+      <c r="H125" s="3">
+        <v>0</v>
+      </c>
+      <c r="I125" s="3">
+        <v>0</v>
+      </c>
+      <c r="J125" s="3">
+        <v>1</v>
+      </c>
+      <c r="K125" s="3">
+        <v>95</v>
+      </c>
+      <c r="L125" s="3">
+        <v>25</v>
+      </c>
+      <c r="M125" s="3">
+        <v>18</v>
+      </c>
+      <c r="N125" s="3">
+        <v>0</v>
+      </c>
+      <c r="O125" s="3">
+        <v>4</v>
+      </c>
+      <c r="P125" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="3">
+        <v>17</v>
+      </c>
+      <c r="R125" s="3">
+        <v>1</v>
+      </c>
+      <c r="S125" s="3">
+        <v>1</v>
+      </c>
+      <c r="T125" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:20" ht="18" thickBot="1">
+      <c r="A126" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126" s="4">
+        <v>2</v>
+      </c>
+      <c r="E126" s="3">
+        <v>7.71</v>
+      </c>
+      <c r="F126" s="3">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3">
+        <v>2</v>
+      </c>
+      <c r="H126" s="3">
+        <v>0</v>
+      </c>
+      <c r="I126" s="3">
+        <v>0</v>
+      </c>
+      <c r="J126" s="3">
+        <v>0</v>
+      </c>
+      <c r="K126" s="3">
+        <v>44</v>
+      </c>
+      <c r="L126" s="5">
+        <v>9.3333333333333339</v>
+      </c>
+      <c r="M126" s="3">
+        <v>11</v>
+      </c>
+      <c r="N126" s="3">
+        <v>1</v>
+      </c>
+      <c r="O126" s="3">
+        <v>7</v>
+      </c>
+      <c r="P126" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q126" s="3">
+        <v>8</v>
+      </c>
+      <c r="R126" s="3">
+        <v>11</v>
+      </c>
+      <c r="S126" s="3">
+        <v>8</v>
+      </c>
+      <c r="T126" s="3">
+        <v>0.32400000000000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:20" ht="18" thickBot="1">
+      <c r="A127" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D127" s="4">
+        <v>2</v>
+      </c>
+      <c r="E127" s="3">
+        <v>0</v>
+      </c>
+      <c r="F127" s="3">
+        <v>0</v>
+      </c>
+      <c r="G127" s="3">
+        <v>0</v>
+      </c>
+      <c r="H127" s="3">
+        <v>0</v>
+      </c>
+      <c r="I127" s="3">
+        <v>1</v>
+      </c>
+      <c r="J127" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K127" s="3">
+        <v>10</v>
+      </c>
+      <c r="L127" s="5">
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="M127" s="3">
+        <v>0</v>
+      </c>
+      <c r="N127" s="3">
+        <v>0</v>
+      </c>
+      <c r="O127" s="3">
+        <v>3</v>
+      </c>
+      <c r="P127" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="3">
+        <v>2</v>
+      </c>
+      <c r="R127" s="3">
+        <v>0</v>
+      </c>
+      <c r="S127" s="3">
+        <v>0</v>
+      </c>
+      <c r="T127" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:20" ht="18" thickBot="1">
+      <c r="A128" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" s="4">
+        <v>2</v>
+      </c>
+      <c r="E128" s="3">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3">
+        <v>2</v>
+      </c>
+      <c r="G128" s="3">
+        <v>0</v>
+      </c>
+      <c r="H128" s="3">
+        <v>0</v>
+      </c>
+      <c r="I128" s="3">
+        <v>0</v>
+      </c>
+      <c r="J128" s="3">
+        <v>1</v>
+      </c>
+      <c r="K128" s="3">
+        <v>46</v>
+      </c>
+      <c r="L128" s="3">
+        <v>12</v>
+      </c>
+      <c r="M128" s="3">
+        <v>6</v>
+      </c>
+      <c r="N128" s="3">
+        <v>0</v>
+      </c>
+      <c r="O128" s="3">
+        <v>3</v>
+      </c>
+      <c r="P128" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q128" s="3">
+        <v>15</v>
+      </c>
+      <c r="R128" s="3">
+        <v>0</v>
+      </c>
+      <c r="S128" s="3">
+        <v>0</v>
+      </c>
+      <c r="T128" s="3">
+        <v>0.14599999999999999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:20" ht="18" thickBot="1">
+      <c r="A129" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129" s="4">
+        <v>2</v>
+      </c>
+      <c r="E129" s="3">
+        <v>10.130000000000001</v>
+      </c>
+      <c r="F129" s="3">
+        <v>0</v>
+      </c>
+      <c r="G129" s="3">
+        <v>1</v>
+      </c>
+      <c r="H129" s="3">
+        <v>0</v>
+      </c>
+      <c r="I129" s="3">
+        <v>0</v>
+      </c>
+      <c r="J129" s="3">
+        <v>0</v>
+      </c>
+      <c r="K129" s="3">
+        <v>27</v>
+      </c>
+      <c r="L129" s="5">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="M129" s="3">
+        <v>8</v>
+      </c>
+      <c r="N129" s="3">
+        <v>1</v>
+      </c>
+      <c r="O129" s="3">
+        <v>3</v>
+      </c>
+      <c r="P129" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q129" s="3">
+        <v>3</v>
+      </c>
+      <c r="R129" s="3">
+        <v>7</v>
+      </c>
+      <c r="S129" s="3">
+        <v>6</v>
+      </c>
+      <c r="T129" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+    </row>
+    <row r="130" spans="1:20" ht="18" thickBot="1">
+      <c r="A130" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D130" s="4">
+        <v>2</v>
+      </c>
+      <c r="E130" s="3">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="F130" s="3">
+        <v>0</v>
+      </c>
+      <c r="G130" s="3">
+        <v>0</v>
+      </c>
+      <c r="H130" s="3">
+        <v>0</v>
+      </c>
+      <c r="I130" s="3">
+        <v>0</v>
+      </c>
+      <c r="J130" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K130" s="3">
+        <v>25</v>
+      </c>
+      <c r="L130" s="5">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="M130" s="3">
+        <v>5</v>
+      </c>
+      <c r="N130" s="3">
+        <v>0</v>
+      </c>
+      <c r="O130" s="3">
+        <v>3</v>
+      </c>
+      <c r="P130" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q130" s="3">
+        <v>1</v>
+      </c>
+      <c r="R130" s="3">
+        <v>3</v>
+      </c>
+      <c r="S130" s="3">
+        <v>3</v>
+      </c>
+      <c r="T130" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="131" spans="1:20" ht="18" thickBot="1">
+      <c r="A131" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D131" s="4">
+        <v>2</v>
+      </c>
+      <c r="E131" s="3">
+        <v>64.8</v>
+      </c>
+      <c r="F131" s="3">
+        <v>0</v>
+      </c>
+      <c r="G131" s="3">
+        <v>2</v>
+      </c>
+      <c r="H131" s="3">
+        <v>0</v>
+      </c>
+      <c r="I131" s="3">
+        <v>0</v>
+      </c>
+      <c r="J131" s="3">
+        <v>0</v>
+      </c>
+      <c r="K131" s="3">
+        <v>19</v>
+      </c>
+      <c r="L131" s="5">
+        <v>1.6666666666666665</v>
+      </c>
+      <c r="M131" s="3">
+        <v>13</v>
+      </c>
+      <c r="N131" s="3">
+        <v>1</v>
+      </c>
+      <c r="O131" s="3">
+        <v>1</v>
+      </c>
+      <c r="P131" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q131" s="3">
+        <v>1</v>
+      </c>
+      <c r="R131" s="3">
+        <v>12</v>
+      </c>
+      <c r="S131" s="3">
+        <v>12</v>
+      </c>
+      <c r="T131" s="3">
+        <v>0.81299999999999994</v>
+      </c>
+    </row>
+    <row r="132" spans="1:20" ht="18" thickBot="1">
+      <c r="A132" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D132" s="4">
+        <v>2</v>
+      </c>
+      <c r="E132" s="3">
+        <v>0</v>
+      </c>
+      <c r="F132" s="3">
+        <v>0</v>
+      </c>
+      <c r="G132" s="3">
+        <v>0</v>
+      </c>
+      <c r="H132" s="3">
+        <v>0</v>
+      </c>
+      <c r="I132" s="3">
+        <v>1</v>
+      </c>
+      <c r="J132" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K132" s="3">
+        <v>5</v>
+      </c>
+      <c r="L132" s="5">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="M132" s="3">
+        <v>1</v>
+      </c>
+      <c r="N132" s="3">
+        <v>0</v>
+      </c>
+      <c r="O132" s="3">
+        <v>0</v>
+      </c>
+      <c r="P132" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q132" s="3">
+        <v>1</v>
+      </c>
+      <c r="R132" s="3">
+        <v>0</v>
+      </c>
+      <c r="S132" s="3">
+        <v>0</v>
+      </c>
+      <c r="T132" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:20" ht="18" thickBot="1">
+      <c r="A133" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D133" s="4">
+        <v>2</v>
+      </c>
+      <c r="E133" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="F133" s="3">
+        <v>0</v>
+      </c>
+      <c r="G133" s="3">
+        <v>0</v>
+      </c>
+      <c r="H133" s="3">
+        <v>0</v>
+      </c>
+      <c r="I133" s="3">
+        <v>0</v>
+      </c>
+      <c r="J133" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K133" s="3">
+        <v>11</v>
+      </c>
+      <c r="L133" s="3">
+        <v>2</v>
+      </c>
+      <c r="M133" s="3">
+        <v>5</v>
+      </c>
+      <c r="N133" s="3">
+        <v>1</v>
+      </c>
+      <c r="O133" s="3">
+        <v>0</v>
+      </c>
+      <c r="P133" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q133" s="3">
+        <v>2</v>
+      </c>
+      <c r="R133" s="3">
+        <v>1</v>
+      </c>
+      <c r="S133" s="3">
+        <v>1</v>
+      </c>
+      <c r="T133" s="3">
+        <v>0.45500000000000002</v>
+      </c>
+    </row>
+    <row r="134" spans="1:20" ht="18" thickBot="1">
+      <c r="A134" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D134" s="4">
+        <v>1</v>
+      </c>
+      <c r="E134" s="3">
+        <v>0</v>
+      </c>
+      <c r="F134" s="3">
+        <v>0</v>
+      </c>
+      <c r="G134" s="3">
+        <v>0</v>
+      </c>
+      <c r="H134" s="3">
+        <v>0</v>
+      </c>
+      <c r="I134" s="3">
+        <v>0</v>
+      </c>
+      <c r="J134" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K134" s="3">
+        <v>3</v>
+      </c>
+      <c r="L134" s="3">
+        <v>1</v>
+      </c>
+      <c r="M134" s="3">
+        <v>0</v>
+      </c>
+      <c r="N134" s="3">
+        <v>0</v>
+      </c>
+      <c r="O134" s="3">
+        <v>0</v>
+      </c>
+      <c r="P134" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q134" s="3">
+        <v>2</v>
+      </c>
+      <c r="R134" s="3">
+        <v>0</v>
+      </c>
+      <c r="S134" s="3">
+        <v>0</v>
+      </c>
+      <c r="T134" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:20" ht="18" thickBot="1">
+      <c r="A135" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D135" s="4">
+        <v>1</v>
+      </c>
+      <c r="E135" s="3">
+        <v>0</v>
+      </c>
+      <c r="F135" s="3">
+        <v>0</v>
+      </c>
+      <c r="G135" s="3">
+        <v>0</v>
+      </c>
+      <c r="H135" s="3">
+        <v>0</v>
+      </c>
+      <c r="I135" s="3">
+        <v>0</v>
+      </c>
+      <c r="J135" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K135" s="3">
+        <v>4</v>
+      </c>
+      <c r="L135" s="3">
+        <v>1</v>
+      </c>
+      <c r="M135" s="3">
+        <v>0</v>
+      </c>
+      <c r="N135" s="3">
+        <v>0</v>
+      </c>
+      <c r="O135" s="3">
+        <v>1</v>
+      </c>
+      <c r="P135" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q135" s="3">
+        <v>2</v>
+      </c>
+      <c r="R135" s="3">
+        <v>0</v>
+      </c>
+      <c r="S135" s="3">
+        <v>0</v>
+      </c>
+      <c r="T135" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:20" ht="18" thickBot="1">
+      <c r="A136" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D136" s="4">
+        <v>1</v>
+      </c>
+      <c r="E136" s="3">
+        <v>1.29</v>
+      </c>
+      <c r="F136" s="3">
+        <v>1</v>
+      </c>
+      <c r="G136" s="3">
+        <v>0</v>
+      </c>
+      <c r="H136" s="3">
+        <v>0</v>
+      </c>
+      <c r="I136" s="3">
+        <v>0</v>
+      </c>
+      <c r="J136" s="3">
+        <v>1</v>
+      </c>
+      <c r="K136" s="3">
+        <v>28</v>
+      </c>
+      <c r="L136" s="3">
+        <v>7</v>
+      </c>
+      <c r="M136" s="3">
+        <v>3</v>
+      </c>
+      <c r="N136" s="3">
+        <v>0</v>
+      </c>
+      <c r="O136" s="3">
+        <v>3</v>
+      </c>
+      <c r="P136" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q136" s="3">
+        <v>4</v>
+      </c>
+      <c r="R136" s="3">
+        <v>1</v>
+      </c>
+      <c r="S136" s="3">
+        <v>1</v>
+      </c>
+      <c r="T136" s="3">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="137" spans="1:20" ht="18" thickBot="1">
+      <c r="A137" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D137" s="4">
+        <v>1</v>
+      </c>
+      <c r="E137" s="3">
+        <v>0</v>
+      </c>
+      <c r="F137" s="3">
+        <v>0</v>
+      </c>
+      <c r="G137" s="3">
+        <v>0</v>
+      </c>
+      <c r="H137" s="3">
+        <v>0</v>
+      </c>
+      <c r="I137" s="3">
+        <v>0</v>
+      </c>
+      <c r="J137" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K137" s="3">
+        <v>2</v>
+      </c>
+      <c r="L137" s="8">
+        <v>46025</v>
+      </c>
+      <c r="M137" s="3">
+        <v>1</v>
+      </c>
+      <c r="N137" s="3">
+        <v>0</v>
+      </c>
+      <c r="O137" s="3">
+        <v>0</v>
+      </c>
+      <c r="P137" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q137" s="3">
+        <v>1</v>
+      </c>
+      <c r="R137" s="3">
+        <v>0</v>
+      </c>
+      <c r="S137" s="3">
+        <v>0</v>
+      </c>
+      <c r="T137" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:20" ht="18" thickBot="1">
+      <c r="A138" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D138" s="4">
+        <v>1</v>
+      </c>
+      <c r="E138" s="3">
+        <v>0</v>
+      </c>
+      <c r="F138" s="3">
+        <v>0</v>
+      </c>
+      <c r="G138" s="3">
+        <v>0</v>
+      </c>
+      <c r="H138" s="3">
+        <v>0</v>
+      </c>
+      <c r="I138" s="3">
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K138" s="3">
+        <v>4</v>
+      </c>
+      <c r="L138" s="8">
+        <v>46056</v>
+      </c>
+      <c r="M138" s="3">
+        <v>1</v>
+      </c>
+      <c r="N138" s="3">
+        <v>0</v>
+      </c>
+      <c r="O138" s="3">
+        <v>1</v>
+      </c>
+      <c r="P138" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q138" s="3">
+        <v>0</v>
+      </c>
+      <c r="R138" s="3">
+        <v>0</v>
+      </c>
+      <c r="S138" s="3">
+        <v>0</v>
+      </c>
+      <c r="T138" s="3">
+        <v>0.33300000000000002</v>
+      </c>
+    </row>
+    <row r="139" spans="1:20" ht="18" thickBot="1">
+      <c r="A139" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D139" s="4">
+        <v>1</v>
+      </c>
+      <c r="E139" s="3">
+        <v>54</v>
+      </c>
+      <c r="F139" s="3">
+        <v>0</v>
+      </c>
+      <c r="G139" s="3">
+        <v>0</v>
+      </c>
+      <c r="H139" s="3">
+        <v>0</v>
+      </c>
+      <c r="I139" s="3">
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K139" s="3">
+        <v>5</v>
+      </c>
+      <c r="L139" s="8">
+        <v>46025</v>
+      </c>
+      <c r="M139" s="3">
+        <v>3</v>
+      </c>
+      <c r="N139" s="3">
+        <v>0</v>
+      </c>
+      <c r="O139" s="3">
+        <v>1</v>
+      </c>
+      <c r="P139" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q139" s="3">
+        <v>0</v>
+      </c>
+      <c r="R139" s="3">
+        <v>2</v>
+      </c>
+      <c r="S139" s="3">
+        <v>2</v>
+      </c>
+      <c r="T139" s="3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20" ht="18" thickBot="1">
+      <c r="A140" s="3">
+        <v>2021</v>
+      </c>
+      <c r="B140" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C140" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D140" s="10">
+        <v>1</v>
+      </c>
+      <c r="E140" s="9">
+        <v>18</v>
+      </c>
+      <c r="F140" s="9">
+        <v>0</v>
+      </c>
+      <c r="G140" s="9">
+        <v>0</v>
+      </c>
+      <c r="H140" s="9">
+        <v>0</v>
+      </c>
+      <c r="I140" s="9">
+        <v>0</v>
+      </c>
+      <c r="J140" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K140" s="9">
+        <v>13</v>
+      </c>
+      <c r="L140" s="9">
+        <v>2</v>
+      </c>
+      <c r="M140" s="9">
+        <v>2</v>
+      </c>
+      <c r="N140" s="9">
+        <v>1</v>
+      </c>
+      <c r="O140" s="9">
+        <v>5</v>
+      </c>
+      <c r="P140" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q140" s="9">
+        <v>4</v>
+      </c>
+      <c r="R140" s="9">
+        <v>4</v>
+      </c>
+      <c r="S140" s="9">
+        <v>4</v>
+      </c>
+      <c r="T140" s="9">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1953,6 +9467,91 @@
     <hyperlink ref="R1" r:id="rId15" tooltip="실점" display="javascript:sort('R_CN');" xr:uid="{583B7E2A-443D-4913-9673-2B9575A387C2}"/>
     <hyperlink ref="S1" r:id="rId16" tooltip="자책점" display="javascript:sort('ER_CN');" xr:uid="{72952B7B-4E2D-4141-B4C2-EA0BD1CB94AB}"/>
     <hyperlink ref="T1" r:id="rId17" tooltip="피안타율" display="javascript:sort('OAVG_RT');" xr:uid="{5A140805-6370-4C79-AA66-2086111D3549}"/>
+    <hyperlink ref="D22" r:id="rId18" tooltip="경기" display="javascript:sort('GAME_CN');" xr:uid="{B4342AC7-0038-438D-A354-BF69F49555DE}"/>
+    <hyperlink ref="E22" r:id="rId19" tooltip="평균자책점" display="javascript:sort('ERA_RT');" xr:uid="{E44929BA-37F0-4604-9DD1-FC64436C7482}"/>
+    <hyperlink ref="F22" r:id="rId20" tooltip="승리" display="javascript:sort('W_CN');" xr:uid="{F68787F9-7091-44A2-A1D0-5501DED3E12A}"/>
+    <hyperlink ref="G22" r:id="rId21" tooltip="패배" display="javascript:sort('L_CN');" xr:uid="{CCD4A8AD-5B01-4433-B075-132AB48955FA}"/>
+    <hyperlink ref="H22" r:id="rId22" tooltip="세이브" display="javascript:sort('SV_CN');" xr:uid="{DD19F90E-B78C-44FF-914F-A96763E04665}"/>
+    <hyperlink ref="I22" r:id="rId23" tooltip="홀드" display="javascript:sort('HOLD_CN');" xr:uid="{2B35D891-1795-4E65-A4ED-38738F322CEE}"/>
+    <hyperlink ref="J22" r:id="rId24" tooltip="승률" display="javascript:sort('WRA_RT');" xr:uid="{0D0E6820-E34F-4A27-BC30-D36D38D4E521}"/>
+    <hyperlink ref="K22" r:id="rId25" tooltip="타자수" display="javascript:sort('PA_CN');" xr:uid="{FCD8ED34-7DAD-43F8-A16E-895287ADD2FD}"/>
+    <hyperlink ref="L22" r:id="rId26" tooltip="이닝" display="javascript:sort('INN2_CN');" xr:uid="{CE828484-6667-40D3-A34B-0F867CF8E93B}"/>
+    <hyperlink ref="M22" r:id="rId27" tooltip="피안타" display="javascript:sort('HIT_CN');" xr:uid="{6D6280D5-EC74-4F9D-9340-DD5924F8866B}"/>
+    <hyperlink ref="N22" r:id="rId28" tooltip="홈런" display="javascript:sort('HR_CN');" xr:uid="{83FC7271-D814-4963-B38E-1F03CE2D6863}"/>
+    <hyperlink ref="O22" r:id="rId29" tooltip="볼넷" display="javascript:sort('BB_CN');" xr:uid="{846E9111-9ED2-46A8-8B1E-477DC800470C}"/>
+    <hyperlink ref="P22" r:id="rId30" tooltip="사구" display="javascript:sort('HP_CN');" xr:uid="{9ABE67E2-E24C-49DD-8DA4-9416F413DACC}"/>
+    <hyperlink ref="Q22" r:id="rId31" tooltip="삼진" display="javascript:sort('KK_CN');" xr:uid="{D601C260-6652-47A1-8481-08285C738287}"/>
+    <hyperlink ref="R22" r:id="rId32" tooltip="실점" display="javascript:sort('R_CN');" xr:uid="{F9A6F972-453B-4732-978B-F8AEF0C91A3A}"/>
+    <hyperlink ref="S22" r:id="rId33" tooltip="자책점" display="javascript:sort('ER_CN');" xr:uid="{6B0797BA-A1E4-43E2-A752-1576FBAED953}"/>
+    <hyperlink ref="T22" r:id="rId34" tooltip="피안타율" display="javascript:sort('OAVG_RT');" xr:uid="{DA09FECA-0CF2-48C7-9A85-815EEDE62094}"/>
+    <hyperlink ref="D47" r:id="rId35" tooltip="경기" display="javascript:sort('GAME_CN');" xr:uid="{FFA29FF1-E29B-44B7-B9EE-CDDE83E3B3EE}"/>
+    <hyperlink ref="E47" r:id="rId36" tooltip="평균자책점" display="javascript:sort('ERA_RT');" xr:uid="{3B8E66BC-D216-4B30-B9E4-6D96F1D01B7B}"/>
+    <hyperlink ref="F47" r:id="rId37" tooltip="승리" display="javascript:sort('W_CN');" xr:uid="{D5B275BD-266F-4CF2-BABE-A6C1ABF624B2}"/>
+    <hyperlink ref="G47" r:id="rId38" tooltip="패배" display="javascript:sort('L_CN');" xr:uid="{92779452-1E8E-410E-BA14-39C9AEDC71E9}"/>
+    <hyperlink ref="H47" r:id="rId39" tooltip="세이브" display="javascript:sort('SV_CN');" xr:uid="{18151469-9C16-4564-90E9-2A5BD6D6C4D3}"/>
+    <hyperlink ref="I47" r:id="rId40" tooltip="홀드" display="javascript:sort('HOLD_CN');" xr:uid="{E5366757-B3C4-4823-A442-B415EBA03514}"/>
+    <hyperlink ref="J47" r:id="rId41" tooltip="승률" display="javascript:sort('WRA_RT');" xr:uid="{AD4F99B6-0850-4E18-B1BE-917B86E24732}"/>
+    <hyperlink ref="K47" r:id="rId42" tooltip="타자수" display="javascript:sort('PA_CN');" xr:uid="{A05A9138-A663-4C8D-B738-4C3AC9BEF820}"/>
+    <hyperlink ref="L47" r:id="rId43" tooltip="이닝" display="javascript:sort('INN2_CN');" xr:uid="{17C0BCA6-7A2C-4DB0-859A-318E61755394}"/>
+    <hyperlink ref="M47" r:id="rId44" tooltip="피안타" display="javascript:sort('HIT_CN');" xr:uid="{B821FBFC-50A3-4873-80C8-1DC0A03DC237}"/>
+    <hyperlink ref="N47" r:id="rId45" tooltip="홈런" display="javascript:sort('HR_CN');" xr:uid="{B68822FA-5143-47AC-AFD5-B6FD59376A78}"/>
+    <hyperlink ref="O47" r:id="rId46" tooltip="볼넷" display="javascript:sort('BB_CN');" xr:uid="{735FA647-8DC2-460B-98E3-97AED678AFCD}"/>
+    <hyperlink ref="P47" r:id="rId47" tooltip="사구" display="javascript:sort('HP_CN');" xr:uid="{CC93A82D-4A8F-4E89-8D83-CEDCD7FE99E6}"/>
+    <hyperlink ref="Q47" r:id="rId48" tooltip="삼진" display="javascript:sort('KK_CN');" xr:uid="{26FD3F9E-58CC-4020-AE5A-EC59D9AEF6D9}"/>
+    <hyperlink ref="R47" r:id="rId49" tooltip="실점" display="javascript:sort('R_CN');" xr:uid="{00377132-3D12-4E55-9C77-9B12101BD551}"/>
+    <hyperlink ref="S47" r:id="rId50" tooltip="자책점" display="javascript:sort('ER_CN');" xr:uid="{47E29C91-ED5E-40F6-84F3-277F34D58A27}"/>
+    <hyperlink ref="T47" r:id="rId51" tooltip="피안타율" display="javascript:sort('OAVG_RT');" xr:uid="{3D7B5600-20B8-4862-8191-667F20C5DB56}"/>
+    <hyperlink ref="D72" r:id="rId52" tooltip="경기" display="javascript:sort('GAME_CN');" xr:uid="{45AA1D09-AC03-4497-B769-C3928A5CEFAB}"/>
+    <hyperlink ref="E72" r:id="rId53" tooltip="평균자책점" display="javascript:sort('ERA_RT');" xr:uid="{E23241C4-01E3-4A42-BC08-D121F76142E1}"/>
+    <hyperlink ref="F72" r:id="rId54" tooltip="승리" display="javascript:sort('W_CN');" xr:uid="{0EB3B9A1-0D7E-47C0-80DB-76DA5B13AC6F}"/>
+    <hyperlink ref="G72" r:id="rId55" tooltip="패배" display="javascript:sort('L_CN');" xr:uid="{122F32E5-571D-4C86-A815-5970F234C7DB}"/>
+    <hyperlink ref="H72" r:id="rId56" tooltip="세이브" display="javascript:sort('SV_CN');" xr:uid="{9B14B6CE-4BE8-4AB8-B0D8-57F0CBBBCD78}"/>
+    <hyperlink ref="I72" r:id="rId57" tooltip="홀드" display="javascript:sort('HOLD_CN');" xr:uid="{6E3262D3-D9E3-465A-B3B0-4D6585AA98F2}"/>
+    <hyperlink ref="J72" r:id="rId58" tooltip="승률" display="javascript:sort('WRA_RT');" xr:uid="{41F38A6A-9CF3-49CF-AFC4-9DF882521056}"/>
+    <hyperlink ref="K72" r:id="rId59" tooltip="타자수" display="javascript:sort('PA_CN');" xr:uid="{113BF014-33B8-4FF9-8985-B8BB1D221FEE}"/>
+    <hyperlink ref="L72" r:id="rId60" tooltip="이닝" display="javascript:sort('INN2_CN');" xr:uid="{23545DEF-7AF8-4E1F-89B4-E8B60B20CFC9}"/>
+    <hyperlink ref="M72" r:id="rId61" tooltip="피안타" display="javascript:sort('HIT_CN');" xr:uid="{B0423BE9-DC38-4A31-920E-3EE6824A02F0}"/>
+    <hyperlink ref="N72" r:id="rId62" tooltip="홈런" display="javascript:sort('HR_CN');" xr:uid="{B324F95C-C225-4A7C-8F25-377992D14CE4}"/>
+    <hyperlink ref="O72" r:id="rId63" tooltip="볼넷" display="javascript:sort('BB_CN');" xr:uid="{9FBB01AE-8B2C-4B82-B348-905047A6F4DD}"/>
+    <hyperlink ref="P72" r:id="rId64" tooltip="사구" display="javascript:sort('HP_CN');" xr:uid="{ACCE324C-D730-4F12-B033-E2171A209AC2}"/>
+    <hyperlink ref="Q72" r:id="rId65" tooltip="삼진" display="javascript:sort('KK_CN');" xr:uid="{A1DA8B72-8DDC-424C-AA78-47707D9BBE83}"/>
+    <hyperlink ref="R72" r:id="rId66" tooltip="실점" display="javascript:sort('R_CN');" xr:uid="{CB28E67E-1FF0-4D77-B168-F2AC75FF2E40}"/>
+    <hyperlink ref="S72" r:id="rId67" tooltip="자책점" display="javascript:sort('ER_CN');" xr:uid="{8FCF8D30-2ABA-430C-B594-B8118C59E0B3}"/>
+    <hyperlink ref="T72" r:id="rId68" tooltip="피안타율" display="javascript:sort('OAVG_RT');" xr:uid="{CD564608-AF62-4DA3-A96A-61205EC719CF}"/>
+    <hyperlink ref="D92" r:id="rId69" tooltip="경기" display="javascript:sort('GAME_CN');" xr:uid="{101F7842-677B-495D-813C-7BAE6211F940}"/>
+    <hyperlink ref="E92" r:id="rId70" tooltip="평균자책점" display="javascript:sort('ERA_RT');" xr:uid="{107B5EAC-4EB9-41FF-9158-942D600ECD8A}"/>
+    <hyperlink ref="F92" r:id="rId71" tooltip="승리" display="javascript:sort('W_CN');" xr:uid="{D2B75B20-B3FD-4E4A-BF25-30DDC626F4E5}"/>
+    <hyperlink ref="G92" r:id="rId72" tooltip="패배" display="javascript:sort('L_CN');" xr:uid="{F2AF32B2-0217-4C8B-B749-B169E118772E}"/>
+    <hyperlink ref="H92" r:id="rId73" tooltip="세이브" display="javascript:sort('SV_CN');" xr:uid="{16DDA960-F9FF-445D-BB08-E946A81B2168}"/>
+    <hyperlink ref="I92" r:id="rId74" tooltip="홀드" display="javascript:sort('HOLD_CN');" xr:uid="{46202B0D-9E6C-48A9-BAAA-FFA1CF8B95AD}"/>
+    <hyperlink ref="J92" r:id="rId75" tooltip="승률" display="javascript:sort('WRA_RT');" xr:uid="{690BCA52-A301-482A-90AA-1FA8C20580BA}"/>
+    <hyperlink ref="K92" r:id="rId76" tooltip="타자수" display="javascript:sort('PA_CN');" xr:uid="{4C7CC073-AF2D-4A91-8F24-D0628F1FEDA0}"/>
+    <hyperlink ref="L92" r:id="rId77" tooltip="이닝" display="javascript:sort('INN2_CN');" xr:uid="{0E8EBF4A-56B6-4CDE-AA19-B7D0BC36CC22}"/>
+    <hyperlink ref="M92" r:id="rId78" tooltip="피안타" display="javascript:sort('HIT_CN');" xr:uid="{E137FF9E-E221-4B8F-8EC1-AA3830004F81}"/>
+    <hyperlink ref="N92" r:id="rId79" tooltip="홈런" display="javascript:sort('HR_CN');" xr:uid="{1D3D39B9-E772-4627-91EB-8AEF1BBBCD8F}"/>
+    <hyperlink ref="O92" r:id="rId80" tooltip="볼넷" display="javascript:sort('BB_CN');" xr:uid="{2CBB0AC6-13C5-4C00-9EFC-5EC493BBDE8A}"/>
+    <hyperlink ref="P92" r:id="rId81" tooltip="사구" display="javascript:sort('HP_CN');" xr:uid="{B89D6078-A514-4A55-B4D8-D535EA2A5148}"/>
+    <hyperlink ref="Q92" r:id="rId82" tooltip="삼진" display="javascript:sort('KK_CN');" xr:uid="{B2B1743A-714F-4A1D-9254-A2891F4904E5}"/>
+    <hyperlink ref="R92" r:id="rId83" tooltip="실점" display="javascript:sort('R_CN');" xr:uid="{C348D3FA-5D3F-4DAC-9BED-B208FBFE5757}"/>
+    <hyperlink ref="S92" r:id="rId84" tooltip="자책점" display="javascript:sort('ER_CN');" xr:uid="{66DB6A78-38E1-45FB-BF83-E02EDCA7FB68}"/>
+    <hyperlink ref="T92" r:id="rId85" tooltip="피안타율" display="javascript:sort('OAVG_RT');" xr:uid="{7C7E73C1-3681-42B0-8537-C7DD2DAF7E47}"/>
+    <hyperlink ref="D115" r:id="rId86" tooltip="경기" display="javascript:sort('GAME_CN');" xr:uid="{B7F82A3E-7F6A-4BE1-9396-520821F08384}"/>
+    <hyperlink ref="E115" r:id="rId87" tooltip="평균자책점" display="javascript:sort('ERA_RT');" xr:uid="{BD7BAB6D-2522-4080-B2B9-0D8940A90B01}"/>
+    <hyperlink ref="F115" r:id="rId88" tooltip="승리" display="javascript:sort('W_CN');" xr:uid="{EEA247A5-D01C-4CFF-A595-F79F70CCCE07}"/>
+    <hyperlink ref="G115" r:id="rId89" tooltip="패배" display="javascript:sort('L_CN');" xr:uid="{418ED3EE-2283-44E5-9744-C8642E14B130}"/>
+    <hyperlink ref="H115" r:id="rId90" tooltip="세이브" display="javascript:sort('SV_CN');" xr:uid="{FE88D7B1-85AF-4FF9-81FC-9105AF4C6158}"/>
+    <hyperlink ref="I115" r:id="rId91" tooltip="홀드" display="javascript:sort('HOLD_CN');" xr:uid="{E89F7083-71A2-445C-A490-807A03AF0DD0}"/>
+    <hyperlink ref="J115" r:id="rId92" tooltip="승률" display="javascript:sort('WRA_RT');" xr:uid="{A65EDD1E-B034-45AD-933F-6411CB0E1106}"/>
+    <hyperlink ref="K115" r:id="rId93" tooltip="타자수" display="javascript:sort('PA_CN');" xr:uid="{E770B9FC-F22B-4166-95D8-610C679F9009}"/>
+    <hyperlink ref="L115" r:id="rId94" tooltip="이닝" display="javascript:sort('INN2_CN');" xr:uid="{F4FD771D-10CF-4566-9487-F3D1727B121D}"/>
+    <hyperlink ref="M115" r:id="rId95" tooltip="피안타" display="javascript:sort('HIT_CN');" xr:uid="{8E859B4F-F100-4299-8CAA-750025184AFA}"/>
+    <hyperlink ref="N115" r:id="rId96" tooltip="홈런" display="javascript:sort('HR_CN');" xr:uid="{831981DA-FC2C-47CE-B701-A08ADEAB3996}"/>
+    <hyperlink ref="O115" r:id="rId97" tooltip="볼넷" display="javascript:sort('BB_CN');" xr:uid="{42E469A0-52DD-419B-99CE-899C5E9E6F49}"/>
+    <hyperlink ref="P115" r:id="rId98" tooltip="사구" display="javascript:sort('HP_CN');" xr:uid="{1BCCAC7B-B979-47B3-B360-DE199199C9FC}"/>
+    <hyperlink ref="Q115" r:id="rId99" tooltip="삼진" display="javascript:sort('KK_CN');" xr:uid="{F604CA55-7791-4932-B99A-E40E387750D8}"/>
+    <hyperlink ref="R115" r:id="rId100" tooltip="실점" display="javascript:sort('R_CN');" xr:uid="{745D83ED-8226-4FCF-99A6-EACC3547AED6}"/>
+    <hyperlink ref="S115" r:id="rId101" tooltip="자책점" display="javascript:sort('ER_CN');" xr:uid="{1206B19F-45BD-440D-A960-CBF0DEBE6631}"/>
+    <hyperlink ref="T115" r:id="rId102" tooltip="피안타율" display="javascript:sort('OAVG_RT');" xr:uid="{46C722B9-7734-475D-A970-170D848B7A65}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
